--- a/biomodal/upstream/duet-1.5.0_evoC_Bap1_run_6bp/reports/evoC_Bap1_run_duet-evoC_Summary.xlsx
+++ b/biomodal/upstream/duet-1.5.0_evoC_Bap1_run_6bp/reports/evoC_Bap1_run_duet-evoC_Summary.xlsx
@@ -1169,7 +1169,7 @@
     <t>Timestamp:</t>
   </si>
   <si>
-    <t>2026-01-21_11:38:43</t>
+    <t>2026-02-21_01:01:13</t>
   </si>
   <si>
     <t>Sample ID</t>
@@ -2252,16 +2252,16 @@
         <v>31</v>
       </c>
       <c r="B12" s="7">
-        <v>0.989343</v>
+        <v>0.989169</v>
       </c>
       <c r="C12" s="7">
-        <v>0.989579</v>
+        <v>0.989529</v>
       </c>
       <c r="D12" s="7">
-        <v>0.989832</v>
+        <v>0.989994</v>
       </c>
       <c r="E12" s="7">
-        <v>0.989536</v>
+        <v>0.98922</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2269,16 +2269,16 @@
         <v>32</v>
       </c>
       <c r="B13" s="7">
-        <v>0.999031</v>
+        <v>0.999411</v>
       </c>
       <c r="C13" s="7">
-        <v>0.998861</v>
+        <v>0.999129</v>
       </c>
       <c r="D13" s="7">
-        <v>0.998038</v>
+        <v>0.998451</v>
       </c>
       <c r="E13" s="7">
-        <v>0.998487</v>
+        <v>0.998553</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2286,16 +2286,16 @@
         <v>33</v>
       </c>
       <c r="B14" s="7">
-        <v>0.9867359999999999</v>
+        <v>0.986421</v>
       </c>
       <c r="C14" s="7">
-        <v>0.986936</v>
+        <v>0.98685</v>
       </c>
       <c r="D14" s="7">
-        <v>0.9870719999999999</v>
+        <v>0.987251</v>
       </c>
       <c r="E14" s="7">
-        <v>0.986748</v>
+        <v>0.986247</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -2303,16 +2303,16 @@
         <v>34</v>
       </c>
       <c r="B15" s="7">
-        <v>0.997403</v>
+        <v>0.997265</v>
       </c>
       <c r="C15" s="7">
-        <v>0.997366</v>
+        <v>0.997332</v>
       </c>
       <c r="D15" s="7">
-        <v>0.99725</v>
+        <v>0.99727</v>
       </c>
       <c r="E15" s="7">
-        <v>0.997221</v>
+        <v>0.99704</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -2320,16 +2320,16 @@
         <v>35</v>
       </c>
       <c r="B16" s="7">
-        <v>0.999467</v>
+        <v>0.999853</v>
       </c>
       <c r="C16" s="7">
-        <v>0.999653</v>
+        <v>0.99959</v>
       </c>
       <c r="D16" s="7">
-        <v>0.9987740000000001</v>
+        <v>0.999101</v>
       </c>
       <c r="E16" s="7">
-        <v>0.998829</v>
+        <v>0.999252</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2337,16 +2337,16 @@
         <v>36</v>
       </c>
       <c r="B17" s="7">
-        <v>0.999564</v>
+        <v>0.999607</v>
       </c>
       <c r="C17" s="7">
-        <v>0.999208</v>
+        <v>0.999539</v>
       </c>
       <c r="D17" s="7">
-        <v>0.999264</v>
+        <v>0.99935</v>
       </c>
       <c r="E17" s="7">
-        <v>0.999658</v>
+        <v>0.999302</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2354,16 +2354,16 @@
         <v>37</v>
       </c>
       <c r="B18" s="6">
-        <v>0.05545763947976177</v>
+        <v>0.09410874227324334</v>
       </c>
       <c r="C18" s="6">
-        <v>0.05107667600107745</v>
+        <v>0.090760482585019</v>
       </c>
       <c r="D18" s="6">
-        <v>0.05461044963438554</v>
+        <v>0.08871464294241088</v>
       </c>
       <c r="E18" s="6">
-        <v>0.05444783342996143</v>
+        <v>0.1015528814689812</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2371,16 +2371,16 @@
         <v>38</v>
       </c>
       <c r="B19" s="6">
-        <v>0.05326360643036994</v>
+        <v>0.0637473642916687</v>
       </c>
       <c r="C19" s="6">
-        <v>0.0395882818685669</v>
+        <v>0.08187493603520622</v>
       </c>
       <c r="D19" s="6">
-        <v>0.04901960784313725</v>
+        <v>0.05492859282932188</v>
       </c>
       <c r="E19" s="6">
-        <v>0.11698757007068</v>
+        <v>0.06978714919495539</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2397,16 +2397,16 @@
         <v>40</v>
       </c>
       <c r="B21" s="7">
-        <v>0.9863875265975182</v>
+        <v>0.9865979436981649</v>
       </c>
       <c r="C21" s="7">
-        <v>0.9866311379490271</v>
+        <v>0.9864826724945364</v>
       </c>
       <c r="D21" s="7">
-        <v>0.9868631376383133</v>
+        <v>0.9866927411503399</v>
       </c>
       <c r="E21" s="7">
-        <v>0.9872396329305312</v>
+        <v>0.9867882839103044</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2423,16 +2423,16 @@
         <v>42</v>
       </c>
       <c r="B23" s="7">
-        <v>0.99973076937203</v>
+        <v>0.9997473759325066</v>
       </c>
       <c r="C23" s="7">
-        <v>0.9997462632112368</v>
+        <v>0.9997487557898401</v>
       </c>
       <c r="D23" s="7">
-        <v>0.99973282198826</v>
+        <v>0.9997477584685969</v>
       </c>
       <c r="E23" s="7">
-        <v>0.9997425690025447</v>
+        <v>0.9997357939337281</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2440,16 +2440,16 @@
         <v>43</v>
       </c>
       <c r="B24" s="6">
-        <v>35.69875535823461</v>
+        <v>35.97525276576995</v>
       </c>
       <c r="C24" s="6">
-        <v>35.95616560769843</v>
+        <v>35.99903937629527</v>
       </c>
       <c r="D24" s="6">
-        <v>35.73199286364561</v>
+        <v>35.98183405573226</v>
       </c>
       <c r="E24" s="6">
-        <v>35.89339160565703</v>
+        <v>35.78057215040372</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2457,16 +2457,16 @@
         <v>44</v>
       </c>
       <c r="B25" s="7">
-        <v>0.9998580156666381</v>
+        <v>0.9998735308602942</v>
       </c>
       <c r="C25" s="7">
-        <v>0.9998808986353852</v>
+        <v>0.9998814006401933</v>
       </c>
       <c r="D25" s="7">
-        <v>0.9998531545054226</v>
+        <v>0.9998669859812942</v>
       </c>
       <c r="E25" s="7">
-        <v>0.9998934683801221</v>
+        <v>0.9998659767806288</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2474,16 +2474,16 @@
         <v>45</v>
       </c>
       <c r="B26" s="7">
-        <v>0.9996256819032541</v>
+        <v>0.9996154686416379</v>
       </c>
       <c r="C26" s="7">
-        <v>0.999615456710625</v>
+        <v>0.9996039859966183</v>
       </c>
       <c r="D26" s="7">
-        <v>0.9996148743773012</v>
+        <v>0.9996419049840993</v>
       </c>
       <c r="E26" s="7">
-        <v>0.9996258941130698</v>
+        <v>0.9995936972800139</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2491,16 +2491,16 @@
         <v>46</v>
       </c>
       <c r="B27" s="7">
-        <v>0.9998543486121639</v>
+        <v>0.999873944755353</v>
       </c>
       <c r="C27" s="7">
-        <v>0.9998721400886622</v>
+        <v>0.9998712924291968</v>
       </c>
       <c r="D27" s="7">
-        <v>0.9998584975064881</v>
+        <v>0.9998744051342187</v>
       </c>
       <c r="E27" s="7">
-        <v>0.9998709000533403</v>
+        <v>0.9998771703015159</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2508,16 +2508,16 @@
         <v>47</v>
       </c>
       <c r="B28" s="7">
-        <v>0.9995772157976622</v>
+        <v>0.9996144717956651</v>
       </c>
       <c r="C28" s="7">
-        <v>0.9996055925469552</v>
+        <v>0.9996242940910254</v>
       </c>
       <c r="D28" s="7">
-        <v>0.9995955496881102</v>
+        <v>0.9995984552770383</v>
       </c>
       <c r="E28" s="7">
-        <v>0.9995708481415495</v>
+        <v>0.9995925612983549</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2525,16 +2525,16 @@
         <v>48</v>
       </c>
       <c r="B29" s="6">
-        <v>38.47759573291928</v>
+        <v>38.98015435678166</v>
       </c>
       <c r="C29" s="6">
-        <v>39.24083262519914</v>
+        <v>39.25917655264774</v>
       </c>
       <c r="D29" s="6">
-        <v>38.33139373691215</v>
+        <v>38.76102585155219</v>
       </c>
       <c r="E29" s="6">
-        <v>39.7252146921729</v>
+        <v>38.72819954088941</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2542,16 +2542,16 @@
         <v>49</v>
       </c>
       <c r="B30" s="6">
-        <v>34.26759176019664</v>
+        <v>34.15068237895525</v>
       </c>
       <c r="C30" s="6">
-        <v>34.15054763070792</v>
+        <v>34.02289456791934</v>
       </c>
       <c r="D30" s="6">
-        <v>34.14397586475925</v>
+        <v>34.46001723617806</v>
       </c>
       <c r="E30" s="6">
-        <v>34.27005457690088</v>
+        <v>33.91150270287425</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2559,16 +2559,16 @@
         <v>50</v>
       </c>
       <c r="B31" s="6">
-        <v>38.3668537285112</v>
+        <v>38.99439080381154</v>
       </c>
       <c r="C31" s="6">
-        <v>38.93265601055928</v>
+        <v>38.90395906387419</v>
       </c>
       <c r="D31" s="6">
-        <v>38.49235907073266</v>
+        <v>39.01028113850469</v>
       </c>
       <c r="E31" s="6">
-        <v>38.89073937171378</v>
+        <v>39.10696614234149</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2576,16 +2576,16 @@
         <v>51</v>
       </c>
       <c r="B32" s="6">
-        <v>33.73881248814265</v>
+        <v>34.13943844489935</v>
       </c>
       <c r="C32" s="6">
-        <v>34.04054886870717</v>
+        <v>34.25151974447152</v>
       </c>
       <c r="D32" s="6">
-        <v>33.93134825343538</v>
+        <v>33.96266077150398</v>
       </c>
       <c r="E32" s="6">
-        <v>33.67389002414259</v>
+        <v>33.89937720763955</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2602,16 +2602,16 @@
         <v>53</v>
       </c>
       <c r="B34" s="6">
-        <v>99.86837442413811</v>
+        <v>99.8565925728293</v>
       </c>
       <c r="C34" s="6">
-        <v>99.85979310934428</v>
+        <v>99.86181636560393</v>
       </c>
       <c r="D34" s="6">
-        <v>99.7170306860735</v>
+        <v>99.73455759599332</v>
       </c>
       <c r="E34" s="6">
-        <v>99.86760362562379</v>
+        <v>99.85852903483514</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2619,16 +2619,16 @@
         <v>54</v>
       </c>
       <c r="B35" s="6">
-        <v>17.60956811905832</v>
+        <v>17.48670326733721</v>
       </c>
       <c r="C35" s="6">
-        <v>17.30975725033969</v>
+        <v>17.22190882376665</v>
       </c>
       <c r="D35" s="6">
-        <v>17.65351591904033</v>
+        <v>17.53265652293625</v>
       </c>
       <c r="E35" s="6">
-        <v>17.59236941325448</v>
+        <v>17.48162297277229</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2636,16 +2636,16 @@
         <v>55</v>
       </c>
       <c r="B36" s="6">
-        <v>82.390432</v>
+        <v>82.51329699999999</v>
       </c>
       <c r="C36" s="6">
-        <v>82.690243</v>
+        <v>82.778091</v>
       </c>
       <c r="D36" s="6">
-        <v>82.346484</v>
+        <v>82.467343</v>
       </c>
       <c r="E36" s="6">
-        <v>82.40763099999999</v>
+        <v>82.518377</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2653,16 +2653,16 @@
         <v>56</v>
       </c>
       <c r="B37" s="6">
-        <v>71.90405895775676</v>
+        <v>72.09390365517567</v>
       </c>
       <c r="C37" s="6">
-        <v>72.2702911389746</v>
+        <v>72.42784856159264</v>
       </c>
       <c r="D37" s="6">
-        <v>72.43620669978569</v>
+        <v>72.62280332617082</v>
       </c>
       <c r="E37" s="6">
-        <v>72.33649603334071</v>
+        <v>72.51621466136707</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2670,16 +2670,16 @@
         <v>57</v>
       </c>
       <c r="B38" s="6">
-        <v>10.33548549915497</v>
+        <v>10.25157043055693</v>
       </c>
       <c r="C38" s="6">
-        <v>10.27482021311935</v>
+        <v>10.18880322639688</v>
       </c>
       <c r="D38" s="6">
-        <v>9.761860434904206</v>
+        <v>9.679515402753145</v>
       </c>
       <c r="E38" s="6">
-        <v>9.92081885821629</v>
+        <v>9.83422104269024</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2687,16 +2687,16 @@
         <v>58</v>
       </c>
       <c r="B39" s="6">
-        <v>99.93684101982419</v>
+        <v>99.94153681909458</v>
       </c>
       <c r="C39" s="6">
-        <v>99.92966093967775</v>
+        <v>99.92648456809684</v>
       </c>
       <c r="D39" s="6">
-        <v>99.9418822405042</v>
+        <v>99.92998536057539</v>
       </c>
       <c r="E39" s="6">
-        <v>99.92362360677808</v>
+        <v>99.92383757092627</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2704,16 +2704,16 @@
         <v>59</v>
       </c>
       <c r="B40" s="6">
-        <v>99.37014458723489</v>
+        <v>99.37865212034411</v>
       </c>
       <c r="C40" s="6">
-        <v>99.36591670297253</v>
+        <v>99.37455753361819</v>
       </c>
       <c r="D40" s="6">
-        <v>99.34736237343789</v>
+        <v>99.35564206005762</v>
       </c>
       <c r="E40" s="6">
-        <v>99.33679606693168</v>
+        <v>99.3452950967047</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2721,16 +2721,16 @@
         <v>60</v>
       </c>
       <c r="B41" s="6">
-        <v>0.6260659509648527</v>
+        <v>0.6181019614366112</v>
       </c>
       <c r="C41" s="6">
-        <v>0.6305873669715668</v>
+        <v>0.6224358008855703</v>
       </c>
       <c r="D41" s="6">
-        <v>0.6487743059756255</v>
+        <v>0.6410695671046008</v>
       </c>
       <c r="E41" s="6">
-        <v>0.6590455594581772</v>
+        <v>0.6511118698715666</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2738,16 +2738,16 @@
         <v>61</v>
       </c>
       <c r="B42" s="6">
-        <v>99.92740106521269</v>
+        <v>99.92997198879551</v>
       </c>
       <c r="C42" s="6">
-        <v>99.93346524696963</v>
+        <v>99.93068021878925</v>
       </c>
       <c r="D42" s="6">
-        <v>99.94013209563416</v>
+        <v>99.94703636694899</v>
       </c>
       <c r="E42" s="6">
-        <v>99.92040061448151</v>
+        <v>99.92889455294296</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2755,16 +2755,16 @@
         <v>62</v>
       </c>
       <c r="B43" s="6">
-        <v>99.13812135525205</v>
+        <v>99.14556002080204</v>
       </c>
       <c r="C43" s="6">
-        <v>99.13340307535296</v>
+        <v>99.14057081066693</v>
       </c>
       <c r="D43" s="6">
-        <v>99.12312628998923</v>
+        <v>99.12921613106489</v>
       </c>
       <c r="E43" s="6">
-        <v>99.10884293722215</v>
+        <v>99.11509943039002</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2772,16 +2772,16 @@
         <v>63</v>
       </c>
       <c r="B44" s="6">
-        <v>0.8591043803215878</v>
+        <v>0.8519533009766255</v>
       </c>
       <c r="C44" s="6">
-        <v>0.8641337818017085</v>
+        <v>0.8572201533143683</v>
       </c>
       <c r="D44" s="6">
-        <v>0.8740541209189239</v>
+        <v>0.868244526467326</v>
       </c>
       <c r="E44" s="6">
-        <v>0.8881377533470073</v>
+        <v>0.8821680623890857</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2798,16 +2798,16 @@
         <v>65</v>
       </c>
       <c r="B46" s="6">
-        <v>2326</v>
+        <v>12669</v>
       </c>
       <c r="C46" s="6">
-        <v>2794</v>
+        <v>13055</v>
       </c>
       <c r="D46" s="6">
-        <v>9228</v>
+        <v>34315</v>
       </c>
       <c r="E46" s="6">
-        <v>7230</v>
+        <v>32059</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2815,16 +2815,16 @@
         <v>66</v>
       </c>
       <c r="B47" s="6">
-        <v>3998</v>
+        <v>23975</v>
       </c>
       <c r="C47" s="6">
-        <v>4588</v>
+        <v>22955</v>
       </c>
       <c r="D47" s="6">
-        <v>14212</v>
+        <v>69716</v>
       </c>
       <c r="E47" s="6">
-        <v>11408</v>
+        <v>65842</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2832,16 +2832,16 @@
         <v>67</v>
       </c>
       <c r="B48" s="6">
-        <v>2241</v>
+        <v>12279</v>
       </c>
       <c r="C48" s="6">
-        <v>2696</v>
+        <v>12700</v>
       </c>
       <c r="D48" s="6">
-        <v>9105</v>
+        <v>33229</v>
       </c>
       <c r="E48" s="6">
-        <v>7121</v>
+        <v>31134</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -2849,16 +2849,16 @@
         <v>68</v>
       </c>
       <c r="B49" s="6">
-        <v>4083</v>
+        <v>24365</v>
       </c>
       <c r="C49" s="6">
-        <v>4686</v>
+        <v>23310</v>
       </c>
       <c r="D49" s="6">
-        <v>14335</v>
+        <v>70802</v>
       </c>
       <c r="E49" s="6">
-        <v>11517</v>
+        <v>66767</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -2866,16 +2866,16 @@
         <v>69</v>
       </c>
       <c r="B50" s="6">
-        <v>78</v>
+        <v>744</v>
       </c>
       <c r="C50" s="6">
-        <v>120</v>
+        <v>641</v>
       </c>
       <c r="D50" s="6">
-        <v>434</v>
+        <v>1751</v>
       </c>
       <c r="E50" s="6">
-        <v>351</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2883,16 +2883,16 @@
         <v>70</v>
       </c>
       <c r="B51" s="6">
-        <v>6246</v>
+        <v>35900</v>
       </c>
       <c r="C51" s="6">
-        <v>7262</v>
+        <v>35369</v>
       </c>
       <c r="D51" s="6">
-        <v>23006</v>
+        <v>102280</v>
       </c>
       <c r="E51" s="6">
-        <v>18287</v>
+        <v>96279</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -2900,16 +2900,16 @@
         <v>71</v>
       </c>
       <c r="B52" s="6">
-        <v>84854</v>
+        <v>55779</v>
       </c>
       <c r="C52" s="6">
-        <v>80523</v>
+        <v>57130</v>
       </c>
       <c r="D52" s="6">
-        <v>98901</v>
+        <v>50260</v>
       </c>
       <c r="E52" s="6">
-        <v>111029</v>
+        <v>59203</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -2917,16 +2917,16 @@
         <v>72</v>
       </c>
       <c r="B53" s="6">
-        <v>15663</v>
+        <v>29319</v>
       </c>
       <c r="C53" s="6">
-        <v>3724</v>
+        <v>4697</v>
       </c>
       <c r="D53" s="6">
-        <v>15569</v>
+        <v>10534</v>
       </c>
       <c r="E53" s="6">
-        <v>14913</v>
+        <v>12324</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -2934,16 +2934,16 @@
         <v>73</v>
       </c>
       <c r="B54" s="6">
-        <v>26632</v>
+        <v>69847</v>
       </c>
       <c r="C54" s="6">
-        <v>49346</v>
+        <v>105789</v>
       </c>
       <c r="D54" s="6">
-        <v>40861</v>
+        <v>48915</v>
       </c>
       <c r="E54" s="6">
-        <v>42686</v>
+        <v>63241</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -2951,16 +2951,16 @@
         <v>74</v>
       </c>
       <c r="B55" s="6">
-        <v>40537</v>
+        <v>49659</v>
       </c>
       <c r="C55" s="6">
-        <v>44139</v>
+        <v>56106</v>
       </c>
       <c r="D55" s="6">
-        <v>56106</v>
+        <v>59408</v>
       </c>
       <c r="E55" s="6">
-        <v>53617</v>
+        <v>58055</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -2968,16 +2968,16 @@
         <v>75</v>
       </c>
       <c r="B56" s="6">
-        <v>380</v>
+        <v>490</v>
       </c>
       <c r="C56" s="6">
-        <v>65</v>
+        <v>96</v>
       </c>
       <c r="D56" s="6">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="E56" s="6">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -2985,16 +2985,16 @@
         <v>76</v>
       </c>
       <c r="B57" s="6">
-        <v>1458</v>
+        <v>3750</v>
       </c>
       <c r="C57" s="6">
-        <v>1999</v>
+        <v>4786</v>
       </c>
       <c r="D57" s="6">
-        <v>1848</v>
+        <v>3594</v>
       </c>
       <c r="E57" s="6">
-        <v>1620</v>
+        <v>3435</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -3002,16 +3002,16 @@
         <v>77</v>
       </c>
       <c r="B58" s="6">
-        <v>815</v>
+        <v>1045</v>
       </c>
       <c r="C58" s="6">
-        <v>733</v>
+        <v>1008</v>
       </c>
       <c r="D58" s="6">
-        <v>838</v>
+        <v>1066</v>
       </c>
       <c r="E58" s="6">
-        <v>821</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -3028,16 +3028,16 @@
         <v>79</v>
       </c>
       <c r="B60" s="6">
-        <v>231627782</v>
+        <v>524620181</v>
       </c>
       <c r="C60" s="6">
-        <v>229109741</v>
+        <v>465236581</v>
       </c>
       <c r="D60" s="6">
-        <v>294065606</v>
+        <v>681119262</v>
       </c>
       <c r="E60" s="6">
-        <v>255923558</v>
+        <v>573792430</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -3045,16 +3045,16 @@
         <v>80</v>
       </c>
       <c r="B61" s="6">
-        <v>63626170</v>
+        <v>157246602</v>
       </c>
       <c r="C61" s="6">
-        <v>58964378</v>
+        <v>129150791</v>
       </c>
       <c r="D61" s="6">
-        <v>78800445</v>
+        <v>205536201</v>
       </c>
       <c r="E61" s="6">
-        <v>67864681</v>
+        <v>168159014</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -3062,16 +3062,16 @@
         <v>81</v>
       </c>
       <c r="B62" s="7">
-        <v>0.2746914443967693</v>
+        <v>0.2997341842631098</v>
       </c>
       <c r="C62" s="7">
-        <v>0.2573630337262701</v>
+        <v>0.2776023990254541</v>
       </c>
       <c r="D62" s="7">
-        <v>0.2679689273148115</v>
+        <v>0.3017624261520298</v>
       </c>
       <c r="E62" s="7">
-        <v>0.2651755920023587</v>
+        <v>0.2930659332678892</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -3079,16 +3079,16 @@
         <v>82</v>
       </c>
       <c r="B63" s="6">
-        <v>168001612</v>
+        <v>367373579</v>
       </c>
       <c r="C63" s="6">
-        <v>170145363</v>
+        <v>336085790</v>
       </c>
       <c r="D63" s="6">
-        <v>215265161</v>
+        <v>475583061</v>
       </c>
       <c r="E63" s="6">
-        <v>188058877</v>
+        <v>405633416</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -3096,16 +3096,16 @@
         <v>83</v>
       </c>
       <c r="B64" s="6">
-        <v>21781741125</v>
+        <v>47734066780</v>
       </c>
       <c r="C64" s="6">
-        <v>22442051863</v>
+        <v>44399237513</v>
       </c>
       <c r="D64" s="6">
-        <v>27733269512</v>
+        <v>61469646933</v>
       </c>
       <c r="E64" s="6">
-        <v>24621616739</v>
+        <v>53226176282</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -3113,16 +3113,16 @@
         <v>84</v>
       </c>
       <c r="B65" s="7">
-        <v>0.518943</v>
+        <v>0.492412</v>
       </c>
       <c r="C65" s="7">
-        <v>0.532614</v>
+        <v>0.507964</v>
       </c>
       <c r="D65" s="7">
-        <v>0.519968</v>
+        <v>0.488199</v>
       </c>
       <c r="E65" s="7">
-        <v>0.521971</v>
+        <v>0.493674</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -3130,16 +3130,16 @@
         <v>85</v>
       </c>
       <c r="B66" s="6">
-        <v>129.6519769405546</v>
+        <v>129.9333145021842</v>
       </c>
       <c r="C66" s="6">
-        <v>131.8992858065724</v>
+        <v>132.1068573384194</v>
       </c>
       <c r="D66" s="6">
-        <v>128.833060506247</v>
+        <v>129.2511276657938</v>
       </c>
       <c r="E66" s="6">
-        <v>130.9250439637582</v>
+        <v>131.2174347145009</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -3147,16 +3147,16 @@
         <v>86</v>
       </c>
       <c r="B67" s="6">
-        <v>34.43130630651088</v>
+        <v>34.36792207250941</v>
       </c>
       <c r="C67" s="6">
-        <v>34.3534925110426</v>
+        <v>34.29775319058417</v>
       </c>
       <c r="D67" s="6">
-        <v>34.42285710150135</v>
+        <v>34.36041008360024</v>
       </c>
       <c r="E67" s="6">
-        <v>34.39639058651014</v>
+        <v>34.3374136798377</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -3164,16 +3164,16 @@
         <v>87</v>
       </c>
       <c r="B68" s="6">
-        <v>7.974421114288466</v>
+        <v>17.47578990795926</v>
       </c>
       <c r="C68" s="6">
-        <v>8.216223030177323</v>
+        <v>16.25499160547551</v>
       </c>
       <c r="D68" s="6">
-        <v>10.1533765627474</v>
+        <v>22.50464191805733</v>
       </c>
       <c r="E68" s="6">
-        <v>9.01416577349706</v>
+        <v>19.48659283114331</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -3181,16 +3181,16 @@
         <v>88</v>
       </c>
       <c r="B69" s="6">
-        <v>7.92450355451951</v>
+        <v>17.35811860531537</v>
       </c>
       <c r="C69" s="6">
-        <v>8.163326059555954</v>
+        <v>16.1432099887382</v>
       </c>
       <c r="D69" s="6">
-        <v>10.08963863200411</v>
+        <v>22.35301637454326</v>
       </c>
       <c r="E69" s="6">
-        <v>8.956639543413436</v>
+        <v>19.35319649797662</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -3198,16 +3198,16 @@
         <v>89</v>
       </c>
       <c r="B70" s="6">
-        <v>11.31999999999999</v>
+        <v>10.69</v>
       </c>
       <c r="C70" s="6">
-        <v>10.95</v>
+        <v>10.22</v>
       </c>
       <c r="D70" s="6">
-        <v>11.08</v>
+        <v>10.61</v>
       </c>
       <c r="E70" s="6">
-        <v>10.78</v>
+        <v>10.11</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -3215,16 +3215,16 @@
         <v>90</v>
       </c>
       <c r="B71" s="6">
-        <v>88.68000000000001</v>
+        <v>89.31</v>
       </c>
       <c r="C71" s="6">
-        <v>89.05</v>
+        <v>89.78</v>
       </c>
       <c r="D71" s="6">
-        <v>88.92</v>
+        <v>89.39</v>
       </c>
       <c r="E71" s="6">
-        <v>89.22</v>
+        <v>89.89</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -3232,16 +3232,16 @@
         <v>91</v>
       </c>
       <c r="B72" s="6">
-        <v>87.16</v>
+        <v>88.86</v>
       </c>
       <c r="C72" s="6">
-        <v>87.22</v>
+        <v>89.13</v>
       </c>
       <c r="D72" s="6">
-        <v>87.89</v>
+        <v>89.03</v>
       </c>
       <c r="E72" s="6">
-        <v>87.73</v>
+        <v>89.37</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -3249,16 +3249,16 @@
         <v>92</v>
       </c>
       <c r="B73" s="6">
-        <v>76.73</v>
+        <v>87.02</v>
       </c>
       <c r="C73" s="6">
-        <v>76.08</v>
+        <v>86.39</v>
       </c>
       <c r="D73" s="6">
-        <v>81.87</v>
+        <v>87.77</v>
       </c>
       <c r="E73" s="6">
-        <v>78.73999999999999</v>
+        <v>87.51000000000001</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -3266,16 +3266,16 @@
         <v>93</v>
       </c>
       <c r="B74" s="6">
-        <v>38.37</v>
+        <v>79.97</v>
       </c>
       <c r="C74" s="6">
-        <v>40.75</v>
+        <v>76.53</v>
       </c>
       <c r="D74" s="6">
-        <v>56.97</v>
+        <v>83.81</v>
       </c>
       <c r="E74" s="6">
-        <v>47.6</v>
+        <v>81.09999999999999</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -3283,16 +3283,16 @@
         <v>94</v>
       </c>
       <c r="B75" s="6">
-        <v>0.08</v>
+        <v>23.89</v>
       </c>
       <c r="C75" s="6">
-        <v>0.1</v>
+        <v>19.09</v>
       </c>
       <c r="D75" s="6">
-        <v>0.46</v>
+        <v>48.79</v>
       </c>
       <c r="E75" s="6">
-        <v>0.21</v>
+        <v>35.4</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -3300,16 +3300,16 @@
         <v>95</v>
       </c>
       <c r="B76" s="6">
-        <v>0.04</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="C76" s="6">
-        <v>0.04</v>
+        <v>6.02</v>
       </c>
       <c r="D76" s="6">
-        <v>0.08</v>
+        <v>31.08</v>
       </c>
       <c r="E76" s="6">
-        <v>0.06</v>
+        <v>18.09</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -3317,16 +3317,16 @@
         <v>96</v>
       </c>
       <c r="B77" s="6">
-        <v>0.455801</v>
+        <v>0.45096</v>
       </c>
       <c r="C77" s="6">
-        <v>0.455816</v>
+        <v>0.451708</v>
       </c>
       <c r="D77" s="6">
-        <v>0.453285</v>
+        <v>0.448684</v>
       </c>
       <c r="E77" s="6">
-        <v>0.458422</v>
+        <v>0.45364</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -3364,16 +3364,16 @@
         <v>99</v>
       </c>
       <c r="B80" s="6">
-        <v>276893176</v>
+        <v>631556756</v>
       </c>
       <c r="C80" s="6">
-        <v>277781450</v>
+        <v>568035847</v>
       </c>
       <c r="D80" s="6">
-        <v>352118940</v>
+        <v>821386803</v>
       </c>
       <c r="E80" s="6">
-        <v>311274539</v>
+        <v>702597941</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -3381,16 +3381,16 @@
         <v>100</v>
       </c>
       <c r="B81" s="6">
-        <v>37660627709</v>
+        <v>85908429066</v>
       </c>
       <c r="C81" s="6">
-        <v>38284908250</v>
+        <v>78284529530</v>
       </c>
       <c r="D81" s="6">
-        <v>47520710104</v>
+        <v>110844458895</v>
       </c>
       <c r="E81" s="6">
-        <v>42678029380</v>
+        <v>96333319065</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -3398,16 +3398,16 @@
         <v>101</v>
       </c>
       <c r="B82" s="6">
-        <v>240394857</v>
+        <v>545857554</v>
       </c>
       <c r="C82" s="6">
-        <v>241321037</v>
+        <v>491101113</v>
       </c>
       <c r="D82" s="6">
-        <v>307056700</v>
+        <v>713083003</v>
       </c>
       <c r="E82" s="6">
-        <v>269911216</v>
+        <v>606738916</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -3415,16 +3415,16 @@
         <v>102</v>
       </c>
       <c r="B83" s="7">
-        <v>0.8681862820627981</v>
+        <v>0.8643048290025734</v>
       </c>
       <c r="C83" s="7">
-        <v>0.8687442484010361</v>
+        <v>0.8645600723857133</v>
       </c>
       <c r="D83" s="7">
-        <v>0.8720255150148981</v>
+        <v>0.8681451910300536</v>
       </c>
       <c r="E83" s="7">
-        <v>0.8671162661331577</v>
+        <v>0.8635648933676565</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -3432,16 +3432,16 @@
         <v>103</v>
       </c>
       <c r="B84" s="6">
-        <v>36498319</v>
+        <v>85699202</v>
       </c>
       <c r="C84" s="6">
-        <v>36460413</v>
+        <v>76934734</v>
       </c>
       <c r="D84" s="6">
-        <v>45062240</v>
+        <v>108303800</v>
       </c>
       <c r="E84" s="6">
-        <v>41363323</v>
+        <v>95859025</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -3449,16 +3449,16 @@
         <v>104</v>
       </c>
       <c r="B85" s="7">
-        <v>0.1318137179372019</v>
+        <v>0.1356951709974266</v>
       </c>
       <c r="C85" s="7">
-        <v>0.1312557515989639</v>
+        <v>0.1354399276142866</v>
       </c>
       <c r="D85" s="7">
-        <v>0.1279744849851019</v>
+        <v>0.1318548089699464</v>
       </c>
       <c r="E85" s="7">
-        <v>0.1328837338668422</v>
+        <v>0.1364351066323435</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -3466,16 +3466,16 @@
         <v>105</v>
       </c>
       <c r="B86" s="6">
-        <v>31495187</v>
+        <v>71284690</v>
       </c>
       <c r="C86" s="6">
-        <v>31165350</v>
+        <v>63391473</v>
       </c>
       <c r="D86" s="6">
-        <v>38758381</v>
+        <v>89691566</v>
       </c>
       <c r="E86" s="6">
-        <v>35572446</v>
+        <v>79763351</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -3483,16 +3483,16 @@
         <v>106</v>
       </c>
       <c r="B87" s="7">
-        <v>0.862921577292368</v>
+        <v>0.8318010942505626</v>
       </c>
       <c r="C87" s="7">
-        <v>0.8547722704073594</v>
+        <v>0.8239642838045037</v>
       </c>
       <c r="D87" s="7">
-        <v>0.8601077309960623</v>
+        <v>0.8281479135542797</v>
       </c>
       <c r="E87" s="7">
-        <v>0.8599997152066337</v>
+        <v>0.8320901553087985</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -3500,16 +3500,16 @@
         <v>107</v>
       </c>
       <c r="B88" s="6">
-        <v>271890044</v>
+        <v>617142244</v>
       </c>
       <c r="C88" s="6">
-        <v>272486387</v>
+        <v>554492586</v>
       </c>
       <c r="D88" s="6">
-        <v>345815081</v>
+        <v>802774569</v>
       </c>
       <c r="E88" s="6">
-        <v>305483662</v>
+        <v>686502267</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -3517,16 +3517,16 @@
         <v>108</v>
       </c>
       <c r="B89" s="7">
-        <v>0.9819311834539397</v>
+        <v>0.97717622072275</v>
       </c>
       <c r="C89" s="7">
-        <v>0.9809380251993068</v>
+        <v>0.9761577353409528</v>
       </c>
       <c r="D89" s="7">
-        <v>0.9820973589208237</v>
+        <v>0.9773404759706128</v>
       </c>
       <c r="E89" s="7">
-        <v>0.9813962394142361</v>
+        <v>0.9770912024349356</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -3534,16 +3534,16 @@
         <v>109</v>
       </c>
       <c r="B90" s="7">
-        <v>0.9781314395036721</v>
+        <v>0.9613070880183131</v>
       </c>
       <c r="C90" s="7">
-        <v>0.9764993284520526</v>
+        <v>0.9579217675545511</v>
       </c>
       <c r="D90" s="7">
-        <v>0.9790306249506755</v>
+        <v>0.9627340283376307</v>
       </c>
       <c r="E90" s="7">
-        <v>0.9779012743029586</v>
+        <v>0.9614665950970009</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -3551,16 +3551,16 @@
         <v>110</v>
       </c>
       <c r="B91" s="6">
-        <v>5003132</v>
+        <v>14414512</v>
       </c>
       <c r="C91" s="6">
-        <v>5295063</v>
+        <v>13543261</v>
       </c>
       <c r="D91" s="6">
-        <v>6303859</v>
+        <v>18612234</v>
       </c>
       <c r="E91" s="6">
-        <v>5790877</v>
+        <v>16095674</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -3568,16 +3568,16 @@
         <v>111</v>
       </c>
       <c r="B92" s="7">
-        <v>0.01806881654606035</v>
+        <v>0.02282377927724994</v>
       </c>
       <c r="C92" s="7">
-        <v>0.01906197480069314</v>
+        <v>0.02384226465904712</v>
       </c>
       <c r="D92" s="7">
-        <v>0.01790264107917626</v>
+        <v>0.02265952402938716</v>
       </c>
       <c r="E92" s="7">
-        <v>0.01860376058576381</v>
+        <v>0.02290879756506431</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -3585,16 +3585,16 @@
         <v>112</v>
       </c>
       <c r="B93" s="7">
-        <v>0.9533727510978168</v>
+        <v>0.9485702927519994</v>
       </c>
       <c r="C93" s="7">
-        <v>0.9532091347247776</v>
+        <v>0.9483884566304808</v>
       </c>
       <c r="D93" s="7">
-        <v>0.9541077893148648</v>
+        <v>0.9492618777062415</v>
       </c>
       <c r="E93" s="7">
-        <v>0.9527776081211368</v>
+        <v>0.9484375390652902</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -3602,16 +3602,16 @@
         <v>113</v>
       </c>
       <c r="B94" s="7">
-        <v>0.855416</v>
+        <v>0.840631</v>
       </c>
       <c r="C94" s="7">
-        <v>0.866096</v>
+        <v>0.849414</v>
       </c>
       <c r="D94" s="7">
-        <v>0.850072</v>
+        <v>0.835672</v>
       </c>
       <c r="E94" s="7">
-        <v>0.8620370000000001</v>
+        <v>0.847424</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -3628,16 +3628,16 @@
         <v>115</v>
       </c>
       <c r="B96" s="6">
-        <v>277968822</v>
+        <v>641982413</v>
       </c>
       <c r="C96" s="6">
-        <v>279044111</v>
+        <v>578849552</v>
       </c>
       <c r="D96" s="6">
-        <v>353221924</v>
+        <v>833848753</v>
       </c>
       <c r="E96" s="6">
-        <v>312387017</v>
+        <v>714015724</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -3645,16 +3645,16 @@
         <v>116</v>
       </c>
       <c r="B97" s="6">
-        <v>1075646</v>
+        <v>10425657</v>
       </c>
       <c r="C97" s="6">
-        <v>1262661</v>
+        <v>10813705</v>
       </c>
       <c r="D97" s="6">
-        <v>1102984</v>
+        <v>12461950</v>
       </c>
       <c r="E97" s="6">
-        <v>1112478</v>
+        <v>11417783</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -3662,16 +3662,16 @@
         <v>117</v>
       </c>
       <c r="B98" s="6">
-        <v>41973292122</v>
+        <v>96939344363</v>
       </c>
       <c r="C98" s="6">
-        <v>42135660761</v>
+        <v>87406282352</v>
       </c>
       <c r="D98" s="6">
-        <v>53336510524</v>
+        <v>125911161703</v>
       </c>
       <c r="E98" s="6">
-        <v>47170439567</v>
+        <v>107816374324</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -3679,16 +3679,16 @@
         <v>118</v>
       </c>
       <c r="B99" s="6">
-        <v>41973292122</v>
+        <v>96939344363</v>
       </c>
       <c r="C99" s="6">
-        <v>42135660761</v>
+        <v>87406282352</v>
       </c>
       <c r="D99" s="6">
-        <v>53336510524</v>
+        <v>125911161703</v>
       </c>
       <c r="E99" s="6">
-        <v>47170439567</v>
+        <v>107816374324</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -3696,16 +3696,16 @@
         <v>119</v>
       </c>
       <c r="B100" s="6">
-        <v>109616837</v>
+        <v>249580987</v>
       </c>
       <c r="C100" s="6">
-        <v>101104517</v>
+        <v>206848195</v>
       </c>
       <c r="D100" s="6">
-        <v>146765464</v>
+        <v>342276939</v>
       </c>
       <c r="E100" s="6">
-        <v>119753364</v>
+        <v>270131642</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -3713,16 +3713,16 @@
         <v>120</v>
       </c>
       <c r="B101" s="6">
-        <v>116374830</v>
+        <v>265436971</v>
       </c>
       <c r="C101" s="6">
-        <v>108754280</v>
+        <v>222801274</v>
       </c>
       <c r="D101" s="6">
-        <v>154689536</v>
+        <v>361286223</v>
       </c>
       <c r="E101" s="6">
-        <v>127596826</v>
+        <v>288240203</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -3730,16 +3730,16 @@
         <v>121</v>
       </c>
       <c r="B102" s="6">
-        <v>180662</v>
+        <v>390413</v>
       </c>
       <c r="C102" s="6">
-        <v>298796</v>
+        <v>588188</v>
       </c>
       <c r="D102" s="6">
-        <v>208790</v>
+        <v>461771</v>
       </c>
       <c r="E102" s="6">
-        <v>208651</v>
+        <v>439907</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -3747,16 +3747,16 @@
         <v>122</v>
       </c>
       <c r="B103" s="6">
-        <v>1039772</v>
+        <v>10434797</v>
       </c>
       <c r="C103" s="6">
-        <v>1296546</v>
+        <v>10958162</v>
       </c>
       <c r="D103" s="6">
-        <v>1052329</v>
+        <v>12463412</v>
       </c>
       <c r="E103" s="6">
-        <v>1059574</v>
+        <v>11392974</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -3764,16 +3764,16 @@
         <v>123</v>
       </c>
       <c r="B104" s="7">
-        <v>0.99613</v>
+        <v>0.98376</v>
       </c>
       <c r="C104" s="7">
-        <v>0.995475</v>
+        <v>0.9813190000000001</v>
       </c>
       <c r="D104" s="7">
-        <v>0.996877</v>
+        <v>0.985055</v>
       </c>
       <c r="E104" s="7">
-        <v>0.996439</v>
+        <v>0.984009</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -3781,16 +3781,16 @@
         <v>124</v>
       </c>
       <c r="B105" s="7">
-        <v>0.897252</v>
+        <v>0.886208</v>
       </c>
       <c r="C105" s="7">
-        <v>0.9086109999999999</v>
+        <v>0.89564</v>
       </c>
       <c r="D105" s="7">
-        <v>0.89096</v>
+        <v>0.880339</v>
       </c>
       <c r="E105" s="7">
-        <v>0.904762</v>
+        <v>0.893494</v>
       </c>
     </row>
   </sheetData>

--- a/biomodal/upstream/duet-1.5.0_evoC_Bap1_run_6bp/reports/evoC_Bap1_run_duet-evoC_Summary.xlsx
+++ b/biomodal/upstream/duet-1.5.0_evoC_Bap1_run_6bp/reports/evoC_Bap1_run_duet-evoC_Summary.xlsx
@@ -19,7 +19,7 @@
     <author/>
   </authors>
   <commentList>
-    <comment ref="A12" authorId="0">
+    <comment ref="A13" authorId="0">
       <text>
         <r>
           <rPr>
@@ -32,7 +32,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A13" authorId="0">
+    <comment ref="A14" authorId="0">
       <text>
         <r>
           <rPr>
@@ -45,7 +45,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A14" authorId="0">
+    <comment ref="A15" authorId="0">
       <text>
         <r>
           <rPr>
@@ -58,7 +58,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A15" authorId="0">
+    <comment ref="A16" authorId="0">
       <text>
         <r>
           <rPr>
@@ -71,7 +71,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A16" authorId="0">
+    <comment ref="A17" authorId="0">
       <text>
         <r>
           <rPr>
@@ -84,7 +84,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A17" authorId="0">
+    <comment ref="A18" authorId="0">
       <text>
         <r>
           <rPr>
@@ -97,7 +97,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A18" authorId="0">
+    <comment ref="A19" authorId="0">
       <text>
         <r>
           <rPr>
@@ -110,7 +110,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A19" authorId="0">
+    <comment ref="A20" authorId="0">
       <text>
         <r>
           <rPr>
@@ -123,7 +123,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A21" authorId="0">
+    <comment ref="A22" authorId="0">
       <text>
         <r>
           <rPr>
@@ -136,7 +136,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A23" authorId="0">
+    <comment ref="A24" authorId="0">
       <text>
         <r>
           <rPr>
@@ -149,7 +149,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A24" authorId="0">
+    <comment ref="A25" authorId="0">
       <text>
         <r>
           <rPr>
@@ -162,7 +162,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A25" authorId="0">
+    <comment ref="A26" authorId="0">
       <text>
         <r>
           <rPr>
@@ -175,7 +175,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A26" authorId="0">
+    <comment ref="A27" authorId="0">
       <text>
         <r>
           <rPr>
@@ -188,7 +188,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A27" authorId="0">
+    <comment ref="A28" authorId="0">
       <text>
         <r>
           <rPr>
@@ -201,7 +201,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A28" authorId="0">
+    <comment ref="A29" authorId="0">
       <text>
         <r>
           <rPr>
@@ -214,7 +214,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A29" authorId="0">
+    <comment ref="A30" authorId="0">
       <text>
         <r>
           <rPr>
@@ -227,7 +227,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A30" authorId="0">
+    <comment ref="A31" authorId="0">
       <text>
         <r>
           <rPr>
@@ -240,7 +240,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A31" authorId="0">
+    <comment ref="A32" authorId="0">
       <text>
         <r>
           <rPr>
@@ -253,7 +253,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A32" authorId="0">
+    <comment ref="A33" authorId="0">
       <text>
         <r>
           <rPr>
@@ -266,7 +266,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A34" authorId="0">
+    <comment ref="A35" authorId="0">
       <text>
         <r>
           <rPr>
@@ -279,7 +279,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A35" authorId="0">
+    <comment ref="A36" authorId="0">
       <text>
         <r>
           <rPr>
@@ -292,7 +292,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A36" authorId="0">
+    <comment ref="A37" authorId="0">
       <text>
         <r>
           <rPr>
@@ -305,7 +305,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A37" authorId="0">
+    <comment ref="A38" authorId="0">
       <text>
         <r>
           <rPr>
@@ -318,7 +318,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A38" authorId="0">
+    <comment ref="A39" authorId="0">
       <text>
         <r>
           <rPr>
@@ -331,7 +331,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A39" authorId="0">
+    <comment ref="A40" authorId="0">
       <text>
         <r>
           <rPr>
@@ -344,7 +344,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A40" authorId="0">
+    <comment ref="A41" authorId="0">
       <text>
         <r>
           <rPr>
@@ -357,7 +357,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A41" authorId="0">
+    <comment ref="A42" authorId="0">
       <text>
         <r>
           <rPr>
@@ -370,7 +370,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A42" authorId="0">
+    <comment ref="A43" authorId="0">
       <text>
         <r>
           <rPr>
@@ -383,7 +383,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A43" authorId="0">
+    <comment ref="A44" authorId="0">
       <text>
         <r>
           <rPr>
@@ -396,7 +396,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A44" authorId="0">
+    <comment ref="A45" authorId="0">
       <text>
         <r>
           <rPr>
@@ -409,7 +409,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A46" authorId="0">
+    <comment ref="A47" authorId="0">
       <text>
         <r>
           <rPr>
@@ -422,7 +422,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A47" authorId="0">
+    <comment ref="A48" authorId="0">
       <text>
         <r>
           <rPr>
@@ -435,7 +435,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A48" authorId="0">
+    <comment ref="A49" authorId="0">
       <text>
         <r>
           <rPr>
@@ -448,7 +448,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A49" authorId="0">
+    <comment ref="A50" authorId="0">
       <text>
         <r>
           <rPr>
@@ -461,7 +461,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A50" authorId="0">
+    <comment ref="A51" authorId="0">
       <text>
         <r>
           <rPr>
@@ -474,7 +474,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A51" authorId="0">
+    <comment ref="A52" authorId="0">
       <text>
         <r>
           <rPr>
@@ -487,7 +487,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A52" authorId="0">
+    <comment ref="A53" authorId="0">
       <text>
         <r>
           <rPr>
@@ -500,7 +500,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A53" authorId="0">
+    <comment ref="A54" authorId="0">
       <text>
         <r>
           <rPr>
@@ -513,7 +513,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A54" authorId="0">
+    <comment ref="A55" authorId="0">
       <text>
         <r>
           <rPr>
@@ -526,7 +526,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A55" authorId="0">
+    <comment ref="A56" authorId="0">
       <text>
         <r>
           <rPr>
@@ -539,7 +539,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A56" authorId="0">
+    <comment ref="A57" authorId="0">
       <text>
         <r>
           <rPr>
@@ -552,7 +552,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A57" authorId="0">
+    <comment ref="A58" authorId="0">
       <text>
         <r>
           <rPr>
@@ -565,7 +565,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A58" authorId="0">
+    <comment ref="A59" authorId="0">
       <text>
         <r>
           <rPr>
@@ -578,7 +578,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A60" authorId="0">
+    <comment ref="A61" authorId="0">
       <text>
         <r>
           <rPr>
@@ -591,7 +591,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A61" authorId="0">
+    <comment ref="A62" authorId="0">
       <text>
         <r>
           <rPr>
@@ -604,7 +604,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A62" authorId="0">
+    <comment ref="A63" authorId="0">
       <text>
         <r>
           <rPr>
@@ -617,7 +617,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A63" authorId="0">
+    <comment ref="A64" authorId="0">
       <text>
         <r>
           <rPr>
@@ -630,7 +630,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A64" authorId="0">
+    <comment ref="A65" authorId="0">
       <text>
         <r>
           <rPr>
@@ -643,7 +643,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A65" authorId="0">
+    <comment ref="A66" authorId="0">
       <text>
         <r>
           <rPr>
@@ -656,7 +656,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A66" authorId="0">
+    <comment ref="A67" authorId="0">
       <text>
         <r>
           <rPr>
@@ -669,7 +669,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A67" authorId="0">
+    <comment ref="A68" authorId="0">
       <text>
         <r>
           <rPr>
@@ -682,7 +682,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A68" authorId="0">
+    <comment ref="A69" authorId="0">
       <text>
         <r>
           <rPr>
@@ -695,7 +695,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A69" authorId="0">
+    <comment ref="A70" authorId="0">
       <text>
         <r>
           <rPr>
@@ -708,7 +708,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A70" authorId="0">
+    <comment ref="A71" authorId="0">
       <text>
         <r>
           <rPr>
@@ -721,7 +721,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A71" authorId="0">
+    <comment ref="A72" authorId="0">
       <text>
         <r>
           <rPr>
@@ -734,7 +734,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A72" authorId="0">
+    <comment ref="A73" authorId="0">
       <text>
         <r>
           <rPr>
@@ -747,7 +747,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A73" authorId="0">
+    <comment ref="A74" authorId="0">
       <text>
         <r>
           <rPr>
@@ -760,7 +760,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A74" authorId="0">
+    <comment ref="A75" authorId="0">
       <text>
         <r>
           <rPr>
@@ -773,7 +773,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A75" authorId="0">
+    <comment ref="A76" authorId="0">
       <text>
         <r>
           <rPr>
@@ -786,7 +786,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A76" authorId="0">
+    <comment ref="A77" authorId="0">
       <text>
         <r>
           <rPr>
@@ -799,7 +799,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A77" authorId="0">
+    <comment ref="A78" authorId="0">
       <text>
         <r>
           <rPr>
@@ -812,7 +812,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A78" authorId="0">
+    <comment ref="A79" authorId="0">
       <text>
         <r>
           <rPr>
@@ -825,7 +825,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A80" authorId="0">
+    <comment ref="A81" authorId="0">
       <text>
         <r>
           <rPr>
@@ -838,7 +838,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A81" authorId="0">
+    <comment ref="A82" authorId="0">
       <text>
         <r>
           <rPr>
@@ -851,7 +851,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A82" authorId="0">
+    <comment ref="A83" authorId="0">
       <text>
         <r>
           <rPr>
@@ -864,7 +864,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A83" authorId="0">
+    <comment ref="A84" authorId="0">
       <text>
         <r>
           <rPr>
@@ -877,7 +877,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A84" authorId="0">
+    <comment ref="A85" authorId="0">
       <text>
         <r>
           <rPr>
@@ -890,7 +890,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A85" authorId="0">
+    <comment ref="A86" authorId="0">
       <text>
         <r>
           <rPr>
@@ -903,7 +903,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A86" authorId="0">
+    <comment ref="A87" authorId="0">
       <text>
         <r>
           <rPr>
@@ -916,7 +916,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A87" authorId="0">
+    <comment ref="A88" authorId="0">
       <text>
         <r>
           <rPr>
@@ -929,7 +929,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A88" authorId="0">
+    <comment ref="A89" authorId="0">
       <text>
         <r>
           <rPr>
@@ -942,7 +942,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A89" authorId="0">
+    <comment ref="A90" authorId="0">
       <text>
         <r>
           <rPr>
@@ -955,7 +955,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A90" authorId="0">
+    <comment ref="A91" authorId="0">
       <text>
         <r>
           <rPr>
@@ -968,7 +968,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A91" authorId="0">
+    <comment ref="A92" authorId="0">
       <text>
         <r>
           <rPr>
@@ -981,7 +981,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A92" authorId="0">
+    <comment ref="A93" authorId="0">
       <text>
         <r>
           <rPr>
@@ -994,7 +994,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A93" authorId="0">
+    <comment ref="A94" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1007,7 +1007,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A94" authorId="0">
+    <comment ref="A95" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1020,7 +1020,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A96" authorId="0">
+    <comment ref="A97" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1033,7 +1033,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A97" authorId="0">
+    <comment ref="A98" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1046,7 +1046,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A98" authorId="0">
+    <comment ref="A99" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1059,7 +1059,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A99" authorId="0">
+    <comment ref="A100" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1072,7 +1072,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A100" authorId="0">
+    <comment ref="A101" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1085,7 +1085,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A101" authorId="0">
+    <comment ref="A102" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1098,7 +1098,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A102" authorId="0">
+    <comment ref="A103" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1111,7 +1111,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A103" authorId="0">
+    <comment ref="A104" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1124,7 +1124,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A104" authorId="0">
+    <comment ref="A105" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1137,7 +1137,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A105" authorId="0">
+    <comment ref="A106" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1155,7 +1155,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="132">
   <si>
     <t xml:space="preserve">duet multiomics solution - delivers highly accurate genetic and epigenetic data from a single sample in a single run. </t>
   </si>
@@ -1169,7 +1169,7 @@
     <t>Timestamp:</t>
   </si>
   <si>
-    <t>2026-02-21_01:01:13</t>
+    <t>2026-03-29_17:44:21</t>
   </si>
   <si>
     <t>Sample ID</t>
@@ -1178,16 +1178,37 @@
     <t>evoC-Bap1-ctrl-F</t>
   </si>
   <si>
+    <t>evoC-Bap1-ctrl-F-B2</t>
+  </si>
+  <si>
     <t>evoC-Bap1-ctrl-M</t>
   </si>
   <si>
+    <t>evoC-Bap1-ctrl-M-B2</t>
+  </si>
+  <si>
     <t>evoC-Bap1-mut-F</t>
   </si>
   <si>
+    <t>evoC-Bap1-mut-F-B2</t>
+  </si>
+  <si>
     <t>evoC-Bap1-mut-M</t>
   </si>
   <si>
+    <t>evoC-Bap1-mut-M-B2</t>
+  </si>
+  <si>
     <t>Experimental Data</t>
+  </si>
+  <si>
+    <t>batch</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>2</t>
   </si>
   <si>
     <t>condition</t>
@@ -1723,8 +1744,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A5:A10" totalsRowShown="0">
-  <autoFilter ref="A5:A10"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A5:A11" totalsRowShown="0">
+  <autoFilter ref="A5:A11"/>
   <tableColumns count="1">
     <tableColumn id="1" name="Experimental Data"/>
   </tableColumns>
@@ -1733,8 +1754,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A11:A19" totalsRowShown="0">
-  <autoFilter ref="A11:A19"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A12:A20" totalsRowShown="0">
+  <autoFilter ref="A12:A20"/>
   <tableColumns count="1">
     <tableColumn id="1" name="Modified Cytosine Accuracy: Control DNA (Methylated Lambda Phage &amp; Unmethylated pUC19)"/>
   </tableColumns>
@@ -1743,8 +1764,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A20:A21" totalsRowShown="0">
-  <autoFilter ref="A20:A21"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A21:A22" totalsRowShown="0">
+  <autoFilter ref="A21:A22"/>
   <tableColumns count="1">
     <tableColumn id="1" name="SQ2hmC (Hydroxymethylated Oligo) Control Accuracy"/>
   </tableColumns>
@@ -1753,8 +1774,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A22:A32" totalsRowShown="0">
-  <autoFilter ref="A22:A32"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A23:A33" totalsRowShown="0">
+  <autoFilter ref="A23:A33"/>
   <tableColumns count="1">
     <tableColumn id="1" name="Genetic Accuracy: Control DNA (Lambda Phage)"/>
   </tableColumns>
@@ -1763,8 +1784,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A33:A44" totalsRowShown="0">
-  <autoFilter ref="A33:A44"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A34:A45" totalsRowShown="0">
+  <autoFilter ref="A34:A45"/>
   <tableColumns count="1">
     <tableColumn id="1" name="Quantification of Modified Cytosines"/>
   </tableColumns>
@@ -1773,8 +1794,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A45:A58" totalsRowShown="0">
-  <autoFilter ref="A45:A58"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A46:A59" totalsRowShown="0">
+  <autoFilter ref="A46:A59"/>
   <tableColumns count="1">
     <tableColumn id="1" name="Allele-specific methylation"/>
   </tableColumns>
@@ -1783,8 +1804,8 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Table7" displayName="Table7" ref="A59:A78" totalsRowShown="0">
-  <autoFilter ref="A59:A78"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Table7" displayName="Table7" ref="A60:A79" totalsRowShown="0">
+  <autoFilter ref="A60:A79"/>
   <tableColumns count="1">
     <tableColumn id="1" name="Genome Deduplication &amp; Coverage"/>
   </tableColumns>
@@ -1793,8 +1814,8 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="Table8" displayName="Table8" ref="A79:A94" totalsRowShown="0">
-  <autoFilter ref="A79:A94"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="Table8" displayName="Table8" ref="A80:A95" totalsRowShown="0">
+  <autoFilter ref="A80:A95"/>
   <tableColumns count="1">
     <tableColumn id="1" name="Read Pair Resolution (Prelude)"/>
   </tableColumns>
@@ -1803,8 +1824,8 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="Table9" displayName="Table9" ref="A95:A105" totalsRowShown="0">
-  <autoFilter ref="A95:A105"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="Table9" displayName="Table9" ref="A96:A106" totalsRowShown="0">
+  <autoFilter ref="A96:A106"/>
   <tableColumns count="1">
     <tableColumn id="1" name="Trimming (Prelude)"/>
   </tableColumns>
@@ -2097,14 +2118,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A2:G105"/>
+  <dimension ref="A2:I106"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="60.7109375" customWidth="1"/>
     <col min="2" max="1001" width="40.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:7" ht="102" customHeight="1">
+    <row r="2" spans="1:9" ht="102" customHeight="1">
       <c r="C2" s="1" t="s">
         <v>0</v>
       </c>
@@ -2113,7 +2134,7 @@
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:9">
       <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
@@ -2127,7 +2148,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:9">
       <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
@@ -2143,1654 +2164,2823 @@
       <c r="E4" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" spans="1:7">
+      <c r="F4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="4" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
-    </row>
-    <row r="6" spans="1:7">
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="5" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>17</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="5" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>19</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="5" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+        <v>22</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>24</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="C9" s="6"/>
       <c r="D9" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" s="6" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="10" spans="1:7">
+      <c r="E9" s="6"/>
+      <c r="F9" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="I9" s="6"/>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>29</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="C10" s="6"/>
       <c r="D10" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="7">
+      <c r="E10" s="6"/>
+      <c r="F10" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I10" s="6"/>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="7">
         <v>0.989169</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C13" s="7">
+        <v>0.987182</v>
+      </c>
+      <c r="D13" s="7">
         <v>0.989529</v>
       </c>
-      <c r="D12" s="7">
+      <c r="E13" s="7">
+        <v>0.9865660000000001</v>
+      </c>
+      <c r="F13" s="7">
         <v>0.989994</v>
       </c>
-      <c r="E12" s="7">
+      <c r="G13" s="7">
+        <v>0.987353</v>
+      </c>
+      <c r="H13" s="7">
         <v>0.98922</v>
       </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B13" s="7">
+      <c r="I13" s="7">
+        <v>0.987007</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="7">
         <v>0.999411</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C14" s="7">
+        <v>0.999034</v>
+      </c>
+      <c r="D14" s="7">
         <v>0.999129</v>
       </c>
-      <c r="D13" s="7">
+      <c r="E14" s="7">
+        <v>0.999092</v>
+      </c>
+      <c r="F14" s="7">
         <v>0.998451</v>
       </c>
-      <c r="E13" s="7">
+      <c r="G14" s="7">
+        <v>0.998023</v>
+      </c>
+      <c r="H14" s="7">
         <v>0.998553</v>
       </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B14" s="7">
+      <c r="I14" s="7">
+        <v>0.998206</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="7">
         <v>0.986421</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C15" s="7">
+        <v>0.982432</v>
+      </c>
+      <c r="D15" s="7">
         <v>0.98685</v>
       </c>
-      <c r="D14" s="7">
+      <c r="E15" s="7">
+        <v>0.9827360000000001</v>
+      </c>
+      <c r="F15" s="7">
         <v>0.987251</v>
       </c>
-      <c r="E14" s="7">
+      <c r="G15" s="7">
+        <v>0.982721</v>
+      </c>
+      <c r="H15" s="7">
         <v>0.986247</v>
       </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B15" s="7">
+      <c r="I15" s="7">
+        <v>0.982386</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="7">
         <v>0.997265</v>
       </c>
-      <c r="C15" s="7">
+      <c r="C16" s="7">
+        <v>0.995266</v>
+      </c>
+      <c r="D16" s="7">
         <v>0.997332</v>
       </c>
-      <c r="D15" s="7">
+      <c r="E16" s="7">
+        <v>0.996187</v>
+      </c>
+      <c r="F16" s="7">
         <v>0.99727</v>
       </c>
-      <c r="E15" s="7">
+      <c r="G16" s="7">
+        <v>0.995381</v>
+      </c>
+      <c r="H16" s="7">
         <v>0.99704</v>
       </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B16" s="7">
+      <c r="I16" s="7">
+        <v>0.995393</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B17" s="7">
         <v>0.999853</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C17" s="7">
+        <v>0.999491</v>
+      </c>
+      <c r="D17" s="7">
         <v>0.99959</v>
       </c>
-      <c r="D16" s="7">
+      <c r="E17" s="7">
+        <v>0.999798</v>
+      </c>
+      <c r="F17" s="7">
         <v>0.999101</v>
       </c>
-      <c r="E16" s="7">
+      <c r="G17" s="7">
+        <v>0.99848</v>
+      </c>
+      <c r="H17" s="7">
         <v>0.999252</v>
       </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B17" s="7">
+      <c r="I17" s="7">
+        <v>0.998769</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B18" s="7">
         <v>0.999607</v>
       </c>
-      <c r="C17" s="7">
+      <c r="C18" s="7">
+        <v>0.999542</v>
+      </c>
+      <c r="D18" s="7">
         <v>0.999539</v>
       </c>
-      <c r="D17" s="7">
+      <c r="E18" s="7">
+        <v>0.999294</v>
+      </c>
+      <c r="F18" s="7">
         <v>0.99935</v>
       </c>
-      <c r="E17" s="7">
+      <c r="G18" s="7">
+        <v>0.999544</v>
+      </c>
+      <c r="H18" s="7">
         <v>0.999302</v>
       </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B18" s="6">
+      <c r="I18" s="7">
+        <v>0.999487</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B19" s="6">
         <v>0.09410874227324334</v>
       </c>
-      <c r="C18" s="6">
+      <c r="C19" s="6">
+        <v>0.04244663403215395</v>
+      </c>
+      <c r="D19" s="6">
         <v>0.090760482585019</v>
       </c>
-      <c r="D18" s="6">
+      <c r="E19" s="6">
+        <v>0.03935617336898935</v>
+      </c>
+      <c r="F19" s="6">
         <v>0.08871464294241088</v>
       </c>
-      <c r="E18" s="6">
+      <c r="G19" s="6">
+        <v>0.04042301048487527</v>
+      </c>
+      <c r="H19" s="6">
         <v>0.1015528814689812</v>
       </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B19" s="6">
+      <c r="I19" s="6">
+        <v>0.04670573117190991</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B20" s="6">
         <v>0.0637473642916687</v>
       </c>
-      <c r="C19" s="6">
+      <c r="C20" s="6">
+        <v>0.06098490623570667</v>
+      </c>
+      <c r="D20" s="6">
         <v>0.08187493603520622</v>
       </c>
-      <c r="D19" s="6">
+      <c r="E20" s="6">
+        <v>0.07561627262186824</v>
+      </c>
+      <c r="F20" s="6">
         <v>0.05492859282932188</v>
       </c>
-      <c r="E19" s="6">
+      <c r="G20" s="6">
+        <v>0.09114385538508279</v>
+      </c>
+      <c r="H20" s="6">
         <v>0.06978714919495539</v>
       </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21" s="7">
+      <c r="I20" s="6">
+        <v>0.05636400901824144</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B22" s="7">
         <v>0.9865979436981649</v>
       </c>
-      <c r="C21" s="7">
+      <c r="C22" s="7">
+        <v>0.97942419483309</v>
+      </c>
+      <c r="D22" s="7">
         <v>0.9864826724945364</v>
       </c>
-      <c r="D21" s="7">
+      <c r="E22" s="7">
+        <v>0.9749572079739749</v>
+      </c>
+      <c r="F22" s="7">
         <v>0.9866927411503399</v>
       </c>
-      <c r="E21" s="7">
+      <c r="G22" s="7">
+        <v>0.9788044929811297</v>
+      </c>
+      <c r="H22" s="7">
         <v>0.9867882839103044</v>
       </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B23" s="7">
+      <c r="I22" s="7">
+        <v>0.9799718019179232</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B24" s="7">
         <v>0.9997473759325066</v>
       </c>
-      <c r="C23" s="7">
+      <c r="C24" s="7">
+        <v>0.9997190029552596</v>
+      </c>
+      <c r="D24" s="7">
         <v>0.9997487557898401</v>
       </c>
-      <c r="D23" s="7">
+      <c r="E24" s="7">
+        <v>0.9997091623481323</v>
+      </c>
+      <c r="F24" s="7">
         <v>0.9997477584685969</v>
       </c>
-      <c r="E23" s="7">
+      <c r="G24" s="7">
+        <v>0.9997123634868602</v>
+      </c>
+      <c r="H24" s="7">
         <v>0.9997357939337281</v>
       </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B24" s="6">
+      <c r="I24" s="7">
+        <v>0.9997175484913223</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B25" s="6">
         <v>35.97525276576995</v>
       </c>
-      <c r="C24" s="6">
+      <c r="C25" s="6">
+        <v>35.51298247567138</v>
+      </c>
+      <c r="D25" s="6">
         <v>35.99903937629527</v>
       </c>
-      <c r="D24" s="6">
+      <c r="E25" s="6">
+        <v>35.36349370371987</v>
+      </c>
+      <c r="F25" s="6">
         <v>35.98183405573226</v>
       </c>
-      <c r="E24" s="6">
+      <c r="G25" s="6">
+        <v>35.41155984601407</v>
+      </c>
+      <c r="H25" s="6">
         <v>35.78057215040372</v>
       </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B25" s="7">
+      <c r="I25" s="6">
+        <v>35.49056101194468</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B26" s="7">
         <v>0.9998735308602942</v>
       </c>
-      <c r="C25" s="7">
+      <c r="C26" s="7">
+        <v>0.9998960186005796</v>
+      </c>
+      <c r="D26" s="7">
         <v>0.9998814006401933</v>
       </c>
-      <c r="D25" s="7">
+      <c r="E26" s="7">
+        <v>0.9999029329418295</v>
+      </c>
+      <c r="F26" s="7">
         <v>0.9998669859812942</v>
       </c>
-      <c r="E25" s="7">
+      <c r="G26" s="7">
+        <v>0.9999003357591042</v>
+      </c>
+      <c r="H26" s="7">
         <v>0.9998659767806288</v>
       </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B26" s="7">
+      <c r="I26" s="7">
+        <v>0.9998967211391779</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" s="7">
         <v>0.9996154686416379</v>
       </c>
-      <c r="C26" s="7">
+      <c r="C27" s="7">
+        <v>0.9995581931049576</v>
+      </c>
+      <c r="D27" s="7">
         <v>0.9996039859966183</v>
       </c>
-      <c r="D26" s="7">
+      <c r="E27" s="7">
+        <v>0.9995236347556629</v>
+      </c>
+      <c r="F27" s="7">
         <v>0.9996419049840993</v>
       </c>
-      <c r="E26" s="7">
+      <c r="G27" s="7">
+        <v>0.9995210063221722</v>
+      </c>
+      <c r="H27" s="7">
         <v>0.9995936972800139</v>
       </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B27" s="7">
+      <c r="I27" s="7">
+        <v>0.9995525653715654</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B28" s="7">
         <v>0.999873944755353</v>
       </c>
-      <c r="C27" s="7">
+      <c r="C28" s="7">
+        <v>0.9998612426285146</v>
+      </c>
+      <c r="D28" s="7">
         <v>0.9998712924291968</v>
       </c>
-      <c r="D27" s="7">
+      <c r="E28" s="7">
+        <v>0.999860787379059</v>
+      </c>
+      <c r="F28" s="7">
         <v>0.9998744051342187</v>
       </c>
-      <c r="E27" s="7">
+      <c r="G28" s="7">
+        <v>0.9998654895648056</v>
+      </c>
+      <c r="H28" s="7">
         <v>0.9998771703015159</v>
       </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B28" s="7">
+      <c r="I28" s="7">
+        <v>0.9998594212548787</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B29" s="7">
         <v>0.9996144717956651</v>
       </c>
-      <c r="C28" s="7">
+      <c r="C29" s="7">
+        <v>0.9995460989796671</v>
+      </c>
+      <c r="D29" s="7">
         <v>0.9996242940910254</v>
       </c>
-      <c r="D28" s="7">
+      <c r="E29" s="7">
+        <v>0.9995318569795535</v>
+      </c>
+      <c r="F29" s="7">
         <v>0.9995984552770383</v>
       </c>
-      <c r="E28" s="7">
+      <c r="G29" s="7">
+        <v>0.9995454623314907</v>
+      </c>
+      <c r="H29" s="7">
         <v>0.9995925612983549</v>
       </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B29" s="6">
+      <c r="I29" s="7">
+        <v>0.9995465193986884</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B30" s="6">
         <v>38.98015435678166</v>
       </c>
-      <c r="C29" s="6">
+      <c r="C30" s="6">
+        <v>39.83044341966386</v>
+      </c>
+      <c r="D30" s="6">
         <v>39.25917655264774</v>
       </c>
-      <c r="D29" s="6">
+      <c r="E30" s="6">
+        <v>40.1292813242069</v>
+      </c>
+      <c r="F30" s="6">
         <v>38.76102585155219</v>
       </c>
-      <c r="E29" s="6">
+      <c r="G30" s="6">
+        <v>40.01460636746952</v>
+      </c>
+      <c r="H30" s="6">
         <v>38.72819954088941</v>
       </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B30" s="6">
+      <c r="I30" s="6">
+        <v>39.85988561034236</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B31" s="6">
         <v>34.15068237895525</v>
       </c>
-      <c r="C30" s="6">
+      <c r="C31" s="6">
+        <v>33.54767510611519</v>
+      </c>
+      <c r="D31" s="6">
         <v>34.02289456791934</v>
       </c>
-      <c r="D30" s="6">
+      <c r="E31" s="6">
+        <v>33.22059932208611</v>
+      </c>
+      <c r="F31" s="6">
         <v>34.46001723617806</v>
       </c>
-      <c r="E30" s="6">
+      <c r="G31" s="6">
+        <v>33.19670218741241</v>
+      </c>
+      <c r="H31" s="6">
         <v>33.91150270287425</v>
       </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="B31" s="6">
+      <c r="I31" s="6">
+        <v>33.49270407463191</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B32" s="6">
         <v>38.99439080381154</v>
       </c>
-      <c r="C31" s="6">
+      <c r="C32" s="6">
+        <v>38.57743935697981</v>
+      </c>
+      <c r="D32" s="6">
         <v>38.90395906387419</v>
       </c>
-      <c r="D31" s="6">
+      <c r="E32" s="6">
+        <v>38.56321390037608</v>
+      </c>
+      <c r="F32" s="6">
         <v>39.01028113850469</v>
       </c>
-      <c r="E31" s="6">
+      <c r="G32" s="6">
+        <v>38.71244022192768</v>
+      </c>
+      <c r="H32" s="6">
         <v>39.10696614234149</v>
       </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="B32" s="6">
+      <c r="I32" s="6">
+        <v>38.52080337739604</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B33" s="6">
         <v>34.13943844489935</v>
       </c>
-      <c r="C32" s="6">
+      <c r="C33" s="6">
+        <v>33.43038840997036</v>
+      </c>
+      <c r="D33" s="6">
         <v>34.25151974447152</v>
       </c>
-      <c r="D32" s="6">
+      <c r="E33" s="6">
+        <v>33.29621447135683</v>
+      </c>
+      <c r="F33" s="6">
         <v>33.96266077150398</v>
       </c>
-      <c r="E32" s="6">
+      <c r="G33" s="6">
+        <v>33.42430120037469</v>
+      </c>
+      <c r="H33" s="6">
         <v>33.89937720763955</v>
       </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
-      <c r="E33" s="4"/>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B34" s="6">
+      <c r="I33" s="6">
+        <v>33.43441286164054</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B35" s="6">
         <v>99.8565925728293</v>
       </c>
-      <c r="C34" s="6">
+      <c r="C35" s="6">
+        <v>99.879419202492</v>
+      </c>
+      <c r="D35" s="6">
         <v>99.86181636560393</v>
       </c>
-      <c r="D34" s="6">
+      <c r="E35" s="6">
+        <v>99.8760676603584</v>
+      </c>
+      <c r="F35" s="6">
         <v>99.73455759599332</v>
       </c>
-      <c r="E34" s="6">
+      <c r="G35" s="6">
+        <v>99.90922996755812</v>
+      </c>
+      <c r="H35" s="6">
         <v>99.85852903483514</v>
       </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="B35" s="6">
+      <c r="I35" s="6">
+        <v>99.86347895578051</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B36" s="6">
         <v>17.48670326733721</v>
       </c>
-      <c r="C35" s="6">
+      <c r="C36" s="6">
+        <v>17.39835241485649</v>
+      </c>
+      <c r="D36" s="6">
         <v>17.22190882376665</v>
       </c>
-      <c r="D35" s="6">
+      <c r="E36" s="6">
+        <v>17.6328448866374</v>
+      </c>
+      <c r="F36" s="6">
         <v>17.53265652293625</v>
       </c>
-      <c r="E35" s="6">
+      <c r="G36" s="6">
+        <v>17.5978983698211</v>
+      </c>
+      <c r="H36" s="6">
         <v>17.48162297277229</v>
       </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B36" s="6">
+      <c r="I36" s="6">
+        <v>17.44172886411982</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B37" s="6">
         <v>82.51329699999999</v>
       </c>
-      <c r="C36" s="6">
+      <c r="C37" s="6">
+        <v>82.601648</v>
+      </c>
+      <c r="D37" s="6">
         <v>82.778091</v>
       </c>
-      <c r="D36" s="6">
+      <c r="E37" s="6">
+        <v>82.367155</v>
+      </c>
+      <c r="F37" s="6">
         <v>82.467343</v>
       </c>
-      <c r="E36" s="6">
+      <c r="G37" s="6">
+        <v>82.402102</v>
+      </c>
+      <c r="H37" s="6">
         <v>82.518377</v>
       </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B37" s="6">
+      <c r="I37" s="6">
+        <v>82.558271</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B38" s="6">
         <v>72.09390365517567</v>
       </c>
-      <c r="C37" s="6">
+      <c r="C38" s="6">
+        <v>72.20956420492651</v>
+      </c>
+      <c r="D38" s="6">
         <v>72.42784856159264</v>
       </c>
-      <c r="D37" s="6">
+      <c r="E38" s="6">
+        <v>72.13383066560024</v>
+      </c>
+      <c r="F38" s="6">
         <v>72.62280332617082</v>
       </c>
-      <c r="E37" s="6">
+      <c r="G38" s="6">
+        <v>72.48680847023898</v>
+      </c>
+      <c r="H38" s="6">
         <v>72.51621466136707</v>
       </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="B38" s="6">
+      <c r="I38" s="6">
+        <v>72.50832426349186</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B39" s="6">
         <v>10.25157043055693</v>
       </c>
-      <c r="C38" s="6">
+      <c r="C39" s="6">
+        <v>10.24304329641784</v>
+      </c>
+      <c r="D39" s="6">
         <v>10.18880322639688</v>
       </c>
-      <c r="D38" s="6">
+      <c r="E39" s="6">
+        <v>10.08279683873509</v>
+      </c>
+      <c r="F39" s="6">
         <v>9.679515402753145</v>
       </c>
-      <c r="E38" s="6">
+      <c r="G39" s="6">
+        <v>9.771169949077876</v>
+      </c>
+      <c r="H39" s="6">
         <v>9.83422104269024</v>
       </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="B39" s="6">
+      <c r="I39" s="6">
+        <v>9.903161185056742</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B40" s="6">
         <v>99.94153681909458</v>
       </c>
-      <c r="C39" s="6">
+      <c r="C40" s="6">
+        <v>99.95535543451918</v>
+      </c>
+      <c r="D40" s="6">
         <v>99.92648456809684</v>
       </c>
-      <c r="D39" s="6">
+      <c r="E40" s="6">
+        <v>99.93609733653699</v>
+      </c>
+      <c r="F40" s="6">
         <v>99.92998536057539</v>
       </c>
-      <c r="E39" s="6">
+      <c r="G40" s="6">
+        <v>99.9385261648011</v>
+      </c>
+      <c r="H40" s="6">
         <v>99.92383757092627</v>
       </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B40" s="6">
+      <c r="I40" s="6">
+        <v>99.95179561340082</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B41" s="6">
         <v>99.37865212034411</v>
       </c>
-      <c r="C40" s="6">
+      <c r="C41" s="6">
+        <v>99.37096532750117</v>
+      </c>
+      <c r="D41" s="6">
         <v>99.37455753361819</v>
       </c>
-      <c r="D40" s="6">
+      <c r="E41" s="6">
+        <v>99.35138688954846</v>
+      </c>
+      <c r="F41" s="6">
         <v>99.35564206005762</v>
       </c>
-      <c r="E40" s="6">
+      <c r="G41" s="6">
+        <v>99.33509163503179</v>
+      </c>
+      <c r="H41" s="6">
         <v>99.3452950967047</v>
       </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="B41" s="6">
+      <c r="I41" s="6">
+        <v>99.3110248000059</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B42" s="6">
         <v>0.6181019614366112</v>
       </c>
-      <c r="C41" s="6">
+      <c r="C42" s="6">
+        <v>0.6262364891440949</v>
+      </c>
+      <c r="D42" s="6">
         <v>0.6224358008855703</v>
       </c>
-      <c r="D41" s="6">
+      <c r="E42" s="6">
+        <v>0.645285494899592</v>
+      </c>
+      <c r="F42" s="6">
         <v>0.6410695671046008</v>
       </c>
-      <c r="E41" s="6">
+      <c r="G42" s="6">
+        <v>0.66136330387613</v>
+      </c>
+      <c r="H42" s="6">
         <v>0.6511118698715666</v>
       </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="B42" s="6">
+      <c r="I42" s="6">
+        <v>0.6845756282509069</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
+      <c r="A43" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B43" s="6">
         <v>99.92997198879551</v>
       </c>
-      <c r="C42" s="6">
+      <c r="C43" s="6">
+        <v>99.93591552732821</v>
+      </c>
+      <c r="D43" s="6">
         <v>99.93068021878925</v>
       </c>
-      <c r="D42" s="6">
+      <c r="E43" s="6">
+        <v>99.93089869961983</v>
+      </c>
+      <c r="F43" s="6">
         <v>99.94703636694899</v>
       </c>
-      <c r="E42" s="6">
+      <c r="G43" s="6">
+        <v>99.95400781441302</v>
+      </c>
+      <c r="H43" s="6">
         <v>99.92889455294296</v>
       </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B43" s="6">
+      <c r="I43" s="6">
+        <v>99.93927407213734</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
+      <c r="A44" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B44" s="6">
         <v>99.14556002080204</v>
       </c>
-      <c r="C43" s="6">
+      <c r="C44" s="6">
+        <v>99.14232805423229</v>
+      </c>
+      <c r="D44" s="6">
         <v>99.14057081066693</v>
       </c>
-      <c r="D43" s="6">
+      <c r="E44" s="6">
+        <v>99.11430030552683</v>
+      </c>
+      <c r="F44" s="6">
         <v>99.12921613106489</v>
       </c>
-      <c r="E43" s="6">
+      <c r="G44" s="6">
+        <v>99.11566321200723</v>
+      </c>
+      <c r="H44" s="6">
         <v>99.11509943039002</v>
       </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
+      <c r="I44" s="6">
+        <v>99.08215030377755</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="A45" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B45" s="6">
+        <v>0.8519533009766255</v>
+      </c>
+      <c r="C45" s="6">
+        <v>0.8555749942922946</v>
+      </c>
+      <c r="D45" s="6">
+        <v>0.8572201533143683</v>
+      </c>
+      <c r="E45" s="6">
+        <v>0.8831968428376502</v>
+      </c>
+      <c r="F45" s="6">
+        <v>0.868244526467326</v>
+      </c>
+      <c r="G45" s="6">
+        <v>0.8816031147598505</v>
+      </c>
+      <c r="H45" s="6">
+        <v>0.8821680623890857</v>
+      </c>
+      <c r="I45" s="6">
+        <v>0.9144560793043059</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
+      <c r="A46" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B46" s="4"/>
+      <c r="C46" s="4"/>
+      <c r="D46" s="4"/>
+      <c r="E46" s="4"/>
+      <c r="F46" s="4"/>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="4"/>
+    </row>
+    <row r="47" spans="1:9">
+      <c r="A47" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B47" s="6">
+        <v>12708</v>
+      </c>
+      <c r="C47" s="6">
+        <v>16988</v>
+      </c>
+      <c r="D47" s="6">
+        <v>13085</v>
+      </c>
+      <c r="E47" s="6">
+        <v>22469</v>
+      </c>
+      <c r="F47" s="6">
+        <v>34383</v>
+      </c>
+      <c r="G47" s="6">
+        <v>26968</v>
+      </c>
+      <c r="H47" s="6">
+        <v>32113</v>
+      </c>
+      <c r="I47" s="6">
+        <v>30977</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
+      <c r="A48" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B48" s="6">
+        <v>24001</v>
+      </c>
+      <c r="C48" s="6">
+        <v>33581</v>
+      </c>
+      <c r="D48" s="6">
+        <v>22976</v>
+      </c>
+      <c r="E48" s="6">
+        <v>45614</v>
+      </c>
+      <c r="F48" s="6">
+        <v>69766</v>
+      </c>
+      <c r="G48" s="6">
+        <v>52995</v>
+      </c>
+      <c r="H48" s="6">
+        <v>65876</v>
+      </c>
+      <c r="I48" s="6">
+        <v>66142</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
+      <c r="A49" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B49" s="6">
+        <v>12318</v>
+      </c>
+      <c r="C49" s="6">
+        <v>16439</v>
+      </c>
+      <c r="D49" s="6">
+        <v>12729</v>
+      </c>
+      <c r="E49" s="6">
+        <v>21639</v>
+      </c>
+      <c r="F49" s="6">
+        <v>33295</v>
+      </c>
+      <c r="G49" s="6">
+        <v>26233</v>
+      </c>
+      <c r="H49" s="6">
+        <v>31190</v>
+      </c>
+      <c r="I49" s="6">
+        <v>30068</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
+      <c r="A50" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B50" s="6">
+        <v>24391</v>
+      </c>
+      <c r="C50" s="6">
+        <v>34130</v>
+      </c>
+      <c r="D50" s="6">
+        <v>23332</v>
+      </c>
+      <c r="E50" s="6">
+        <v>46444</v>
+      </c>
+      <c r="F50" s="6">
+        <v>70854</v>
+      </c>
+      <c r="G50" s="6">
+        <v>53730</v>
+      </c>
+      <c r="H50" s="6">
+        <v>66799</v>
+      </c>
+      <c r="I50" s="6">
+        <v>67051</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
+      <c r="A51" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B51" s="6">
+        <v>745</v>
+      </c>
+      <c r="C51" s="6">
+        <v>1172</v>
+      </c>
+      <c r="D51" s="6">
+        <v>643</v>
+      </c>
+      <c r="E51" s="6">
+        <v>1598</v>
+      </c>
+      <c r="F51" s="6">
+        <v>1755</v>
+      </c>
+      <c r="G51" s="6">
+        <v>1382</v>
+      </c>
+      <c r="H51" s="6">
+        <v>1622</v>
+      </c>
+      <c r="I51" s="6">
+        <v>1951</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9">
+      <c r="A52" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B52" s="6">
+        <v>35964</v>
+      </c>
+      <c r="C52" s="6">
+        <v>49397</v>
+      </c>
+      <c r="D52" s="6">
+        <v>35418</v>
+      </c>
+      <c r="E52" s="6">
+        <v>66485</v>
+      </c>
+      <c r="F52" s="6">
+        <v>102394</v>
+      </c>
+      <c r="G52" s="6">
+        <v>78581</v>
+      </c>
+      <c r="H52" s="6">
+        <v>96367</v>
+      </c>
+      <c r="I52" s="6">
+        <v>95168</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
+      <c r="A53" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B53" s="6">
+        <v>56183</v>
+      </c>
+      <c r="C53" s="6">
+        <v>38224</v>
+      </c>
+      <c r="D53" s="6">
+        <v>57737</v>
+      </c>
+      <c r="E53" s="6">
+        <v>44651</v>
+      </c>
+      <c r="F53" s="6">
+        <v>50766</v>
+      </c>
+      <c r="G53" s="6">
+        <v>56956</v>
+      </c>
+      <c r="H53" s="6">
+        <v>59728</v>
+      </c>
+      <c r="I53" s="6">
+        <v>52730</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9">
+      <c r="A54" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B54" s="6">
+        <v>29326</v>
+      </c>
+      <c r="C54" s="6">
+        <v>3508</v>
+      </c>
+      <c r="D54" s="6">
+        <v>4701</v>
+      </c>
+      <c r="E54" s="6">
+        <v>11813</v>
+      </c>
+      <c r="F54" s="6">
+        <v>10537</v>
+      </c>
+      <c r="G54" s="6">
+        <v>11080</v>
+      </c>
+      <c r="H54" s="6">
+        <v>12330</v>
+      </c>
+      <c r="I54" s="6">
+        <v>43806</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9">
+      <c r="A55" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B55" s="6">
+        <v>70200</v>
+      </c>
+      <c r="C55" s="6">
+        <v>46682</v>
+      </c>
+      <c r="D55" s="6">
+        <v>106658</v>
+      </c>
+      <c r="E55" s="6">
+        <v>60497</v>
+      </c>
+      <c r="F55" s="6">
+        <v>49426</v>
+      </c>
+      <c r="G55" s="6">
+        <v>57968</v>
+      </c>
+      <c r="H55" s="6">
+        <v>63718</v>
+      </c>
+      <c r="I55" s="6">
+        <v>29833</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9">
+      <c r="A56" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B56" s="6">
+        <v>49925</v>
+      </c>
+      <c r="C56" s="6">
+        <v>39557</v>
+      </c>
+      <c r="D56" s="6">
+        <v>56448</v>
+      </c>
+      <c r="E56" s="6">
+        <v>47955</v>
+      </c>
+      <c r="F56" s="6">
+        <v>59778</v>
+      </c>
+      <c r="G56" s="6">
+        <v>59995</v>
+      </c>
+      <c r="H56" s="6">
+        <v>58366</v>
+      </c>
+      <c r="I56" s="6">
+        <v>59343</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9">
+      <c r="A57" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B57" s="6">
+        <v>490</v>
+      </c>
+      <c r="C57" s="6">
         <v>63</v>
       </c>
-      <c r="B44" s="6">
-        <v>0.8519533009766255</v>
-      </c>
-      <c r="C44" s="6">
-        <v>0.8572201533143683</v>
-      </c>
-      <c r="D44" s="6">
-        <v>0.868244526467326</v>
-      </c>
-      <c r="E44" s="6">
-        <v>0.8821680623890857</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="B45" s="4"/>
-      <c r="C45" s="4"/>
-      <c r="D45" s="4"/>
-      <c r="E45" s="4"/>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="B46" s="6">
-        <v>12669</v>
-      </c>
-      <c r="C46" s="6">
-        <v>13055</v>
-      </c>
-      <c r="D46" s="6">
-        <v>34315</v>
-      </c>
-      <c r="E46" s="6">
-        <v>32059</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="B47" s="6">
-        <v>23975</v>
-      </c>
-      <c r="C47" s="6">
-        <v>22955</v>
-      </c>
-      <c r="D47" s="6">
-        <v>69716</v>
-      </c>
-      <c r="E47" s="6">
-        <v>65842</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B48" s="6">
-        <v>12279</v>
-      </c>
-      <c r="C48" s="6">
-        <v>12700</v>
-      </c>
-      <c r="D48" s="6">
-        <v>33229</v>
-      </c>
-      <c r="E48" s="6">
-        <v>31134</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="B49" s="6">
-        <v>24365</v>
-      </c>
-      <c r="C49" s="6">
-        <v>23310</v>
-      </c>
-      <c r="D49" s="6">
-        <v>70802</v>
-      </c>
-      <c r="E49" s="6">
-        <v>66767</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B50" s="6">
-        <v>744</v>
-      </c>
-      <c r="C50" s="6">
-        <v>641</v>
-      </c>
-      <c r="D50" s="6">
-        <v>1751</v>
-      </c>
-      <c r="E50" s="6">
-        <v>1622</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="B51" s="6">
-        <v>35900</v>
-      </c>
-      <c r="C51" s="6">
-        <v>35369</v>
-      </c>
-      <c r="D51" s="6">
-        <v>102280</v>
-      </c>
-      <c r="E51" s="6">
-        <v>96279</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="B52" s="6">
-        <v>55779</v>
-      </c>
-      <c r="C52" s="6">
-        <v>57130</v>
-      </c>
-      <c r="D52" s="6">
-        <v>50260</v>
-      </c>
-      <c r="E52" s="6">
-        <v>59203</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="B53" s="6">
-        <v>29319</v>
-      </c>
-      <c r="C53" s="6">
-        <v>4697</v>
-      </c>
-      <c r="D53" s="6">
-        <v>10534</v>
-      </c>
-      <c r="E53" s="6">
-        <v>12324</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B54" s="6">
-        <v>69847</v>
-      </c>
-      <c r="C54" s="6">
-        <v>105789</v>
-      </c>
-      <c r="D54" s="6">
-        <v>48915</v>
-      </c>
-      <c r="E54" s="6">
-        <v>63241</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="B55" s="6">
-        <v>49659</v>
-      </c>
-      <c r="C55" s="6">
-        <v>56106</v>
-      </c>
-      <c r="D55" s="6">
-        <v>59408</v>
-      </c>
-      <c r="E55" s="6">
-        <v>58055</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="B56" s="6">
-        <v>490</v>
-      </c>
-      <c r="C56" s="6">
+      <c r="D57" s="6">
         <v>96</v>
       </c>
-      <c r="D56" s="6">
+      <c r="E57" s="6">
         <v>126</v>
       </c>
-      <c r="E56" s="6">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="B57" s="6">
-        <v>3750</v>
-      </c>
-      <c r="C57" s="6">
-        <v>4786</v>
-      </c>
-      <c r="D57" s="6">
-        <v>3594</v>
-      </c>
-      <c r="E57" s="6">
-        <v>3435</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
+      <c r="F57" s="6">
+        <v>126</v>
+      </c>
+      <c r="G57" s="6">
+        <v>120</v>
+      </c>
+      <c r="H57" s="6">
+        <v>143</v>
+      </c>
+      <c r="I57" s="6">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9">
       <c r="A58" s="5" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="B58" s="6">
-        <v>1045</v>
+        <v>3849</v>
       </c>
       <c r="C58" s="6">
-        <v>1008</v>
+        <v>3288</v>
       </c>
       <c r="D58" s="6">
-        <v>1066</v>
+        <v>4907</v>
       </c>
       <c r="E58" s="6">
-        <v>1046</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B59" s="4"/>
-      <c r="C59" s="4"/>
-      <c r="D59" s="4"/>
-      <c r="E59" s="4"/>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="B60" s="6">
+        <v>4188</v>
+      </c>
+      <c r="F58" s="6">
+        <v>3737</v>
+      </c>
+      <c r="G58" s="6">
+        <v>3668</v>
+      </c>
+      <c r="H58" s="6">
+        <v>3565</v>
+      </c>
+      <c r="I58" s="6">
+        <v>3191</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9">
+      <c r="A59" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="B59" s="6">
+        <v>1084</v>
+      </c>
+      <c r="C59" s="6">
+        <v>1034</v>
+      </c>
+      <c r="D59" s="6">
+        <v>1033</v>
+      </c>
+      <c r="E59" s="6">
+        <v>1087</v>
+      </c>
+      <c r="F59" s="6">
+        <v>1099</v>
+      </c>
+      <c r="G59" s="6">
+        <v>1125</v>
+      </c>
+      <c r="H59" s="6">
+        <v>1078</v>
+      </c>
+      <c r="I59" s="6">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9">
+      <c r="A60" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B60" s="4"/>
+      <c r="C60" s="4"/>
+      <c r="D60" s="4"/>
+      <c r="E60" s="4"/>
+      <c r="F60" s="4"/>
+      <c r="G60" s="4"/>
+      <c r="H60" s="4"/>
+      <c r="I60" s="4"/>
+    </row>
+    <row r="61" spans="1:9">
+      <c r="A61" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B61" s="6">
         <v>524620181</v>
       </c>
-      <c r="C60" s="6">
+      <c r="C61" s="6">
+        <v>628312746</v>
+      </c>
+      <c r="D61" s="6">
         <v>465236581</v>
       </c>
-      <c r="D60" s="6">
+      <c r="E61" s="6">
+        <v>666259619</v>
+      </c>
+      <c r="F61" s="6">
         <v>681119262</v>
       </c>
-      <c r="E60" s="6">
+      <c r="G61" s="6">
+        <v>589200757</v>
+      </c>
+      <c r="H61" s="6">
         <v>573792430</v>
       </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="B61" s="6">
+      <c r="I61" s="6">
+        <v>715075361</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9">
+      <c r="A62" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B62" s="6">
         <v>157246602</v>
       </c>
-      <c r="C61" s="6">
+      <c r="C62" s="6">
+        <v>196145540</v>
+      </c>
+      <c r="D62" s="6">
         <v>129150791</v>
       </c>
-      <c r="D61" s="6">
+      <c r="E62" s="6">
+        <v>196424525</v>
+      </c>
+      <c r="F62" s="6">
         <v>205536201</v>
       </c>
-      <c r="E61" s="6">
+      <c r="G62" s="6">
+        <v>170626519</v>
+      </c>
+      <c r="H62" s="6">
         <v>168159014</v>
       </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="B62" s="7">
+      <c r="I62" s="6">
+        <v>225667090</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9">
+      <c r="A63" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B63" s="7">
         <v>0.2997341842631098</v>
       </c>
-      <c r="C62" s="7">
+      <c r="C63" s="7">
+        <v>0.3121781966842354</v>
+      </c>
+      <c r="D63" s="7">
         <v>0.2776023990254541</v>
       </c>
-      <c r="D62" s="7">
+      <c r="E63" s="7">
+        <v>0.2948167942322796</v>
+      </c>
+      <c r="F63" s="7">
         <v>0.3017624261520298</v>
       </c>
-      <c r="E62" s="7">
+      <c r="G63" s="7">
+        <v>0.2895897823837996</v>
+      </c>
+      <c r="H63" s="7">
         <v>0.2930659332678892</v>
       </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="B63" s="6">
+      <c r="I63" s="7">
+        <v>0.3155850450285617</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9">
+      <c r="A64" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B64" s="6">
         <v>367373579</v>
       </c>
-      <c r="C63" s="6">
+      <c r="C64" s="6">
+        <v>432167206</v>
+      </c>
+      <c r="D64" s="6">
         <v>336085790</v>
       </c>
-      <c r="D63" s="6">
+      <c r="E64" s="6">
+        <v>469835094</v>
+      </c>
+      <c r="F64" s="6">
         <v>475583061</v>
       </c>
-      <c r="E63" s="6">
+      <c r="G64" s="6">
+        <v>418574238</v>
+      </c>
+      <c r="H64" s="6">
         <v>405633416</v>
       </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="B64" s="6">
+      <c r="I64" s="6">
+        <v>489408271</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9">
+      <c r="A65" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B65" s="6">
         <v>47734066780</v>
       </c>
-      <c r="C64" s="6">
+      <c r="C65" s="6">
+        <v>54631232883</v>
+      </c>
+      <c r="D65" s="6">
         <v>44399237513</v>
       </c>
-      <c r="D64" s="6">
+      <c r="E65" s="6">
+        <v>59036807621</v>
+      </c>
+      <c r="F65" s="6">
         <v>61469646933</v>
       </c>
-      <c r="E64" s="6">
+      <c r="G65" s="6">
+        <v>52779890827</v>
+      </c>
+      <c r="H65" s="6">
         <v>53226176282</v>
       </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="B65" s="7">
+      <c r="I65" s="6">
+        <v>62334485356</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9">
+      <c r="A66" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="B66" s="7">
         <v>0.492412</v>
       </c>
-      <c r="C65" s="7">
+      <c r="C66" s="7">
+        <v>0.469575</v>
+      </c>
+      <c r="D66" s="7">
         <v>0.507964</v>
       </c>
-      <c r="D65" s="7">
+      <c r="E66" s="7">
+        <v>0.472318</v>
+      </c>
+      <c r="F66" s="7">
         <v>0.488199</v>
       </c>
-      <c r="E65" s="7">
+      <c r="G66" s="7">
+        <v>0.4843</v>
+      </c>
+      <c r="H66" s="7">
         <v>0.493674</v>
       </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="B66" s="6">
+      <c r="I66" s="7">
+        <v>0.466583</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9">
+      <c r="A67" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B67" s="6">
         <v>129.9333145021842</v>
       </c>
-      <c r="C66" s="6">
+      <c r="C67" s="6">
+        <v>126.4122592471767</v>
+      </c>
+      <c r="D67" s="6">
         <v>132.1068573384194</v>
       </c>
-      <c r="D66" s="6">
+      <c r="E67" s="6">
+        <v>125.65431653558</v>
+      </c>
+      <c r="F67" s="6">
         <v>129.2511276657938</v>
       </c>
-      <c r="E66" s="6">
+      <c r="G67" s="6">
+        <v>126.094455977962</v>
+      </c>
+      <c r="H67" s="6">
         <v>131.2174347145009</v>
       </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="B67" s="6">
+      <c r="I67" s="6">
+        <v>127.3670451638117</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9">
+      <c r="A68" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="B68" s="6">
         <v>34.36792207250941</v>
       </c>
-      <c r="C67" s="6">
+      <c r="C68" s="6">
+        <v>34.39448532221769</v>
+      </c>
+      <c r="D68" s="6">
         <v>34.29775319058417</v>
       </c>
-      <c r="D67" s="6">
+      <c r="E68" s="6">
+        <v>34.36269648676571</v>
+      </c>
+      <c r="F68" s="6">
         <v>34.36041008360024</v>
       </c>
-      <c r="E67" s="6">
+      <c r="G68" s="6">
+        <v>34.39562118344357</v>
+      </c>
+      <c r="H68" s="6">
         <v>34.3374136798377</v>
       </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="B68" s="6">
+      <c r="I68" s="6">
+        <v>34.37393604363425</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9">
+      <c r="A69" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="B69" s="6">
         <v>17.47578990795926</v>
       </c>
-      <c r="C68" s="6">
+      <c r="C69" s="6">
+        <v>20.0011069688547</v>
+      </c>
+      <c r="D69" s="6">
         <v>16.25499160547551</v>
       </c>
-      <c r="D68" s="6">
+      <c r="E69" s="6">
+        <v>21.61401647157674</v>
+      </c>
+      <c r="F69" s="6">
         <v>22.50464191805733</v>
       </c>
-      <c r="E68" s="6">
+      <c r="G69" s="6">
+        <v>19.32371429021918</v>
+      </c>
+      <c r="H69" s="6">
         <v>19.48659283114331</v>
       </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="B69" s="6">
+      <c r="I69" s="6">
+        <v>22.82154491263931</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9">
+      <c r="A70" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B70" s="6">
         <v>17.35811860531537</v>
       </c>
-      <c r="C69" s="6">
+      <c r="C70" s="6">
+        <v>19.87754183620633</v>
+      </c>
+      <c r="D70" s="6">
         <v>16.1432099887382</v>
       </c>
-      <c r="D69" s="6">
+      <c r="E70" s="6">
+        <v>21.47716744572424</v>
+      </c>
+      <c r="F70" s="6">
         <v>22.35301637454326</v>
       </c>
-      <c r="E69" s="6">
+      <c r="G70" s="6">
+        <v>19.20502048808389</v>
+      </c>
+      <c r="H70" s="6">
         <v>19.35319649797662</v>
       </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="B70" s="6">
+      <c r="I70" s="6">
+        <v>22.68044678395069</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9">
+      <c r="A71" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B71" s="6">
         <v>10.69</v>
       </c>
-      <c r="C70" s="6">
+      <c r="C71" s="6">
+        <v>10.66</v>
+      </c>
+      <c r="D71" s="6">
         <v>10.22</v>
       </c>
-      <c r="D70" s="6">
+      <c r="E71" s="6">
+        <v>10.08</v>
+      </c>
+      <c r="F71" s="6">
         <v>10.61</v>
       </c>
-      <c r="E70" s="6">
+      <c r="G71" s="6">
+        <v>10.68000000000001</v>
+      </c>
+      <c r="H71" s="6">
         <v>10.11</v>
       </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="B71" s="6">
+      <c r="I71" s="6">
+        <v>10.05</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9">
+      <c r="A72" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B72" s="6">
         <v>89.31</v>
       </c>
-      <c r="C71" s="6">
+      <c r="C72" s="6">
+        <v>89.34</v>
+      </c>
+      <c r="D72" s="6">
         <v>89.78</v>
       </c>
-      <c r="D71" s="6">
+      <c r="E72" s="6">
+        <v>89.92</v>
+      </c>
+      <c r="F72" s="6">
         <v>89.39</v>
       </c>
-      <c r="E71" s="6">
+      <c r="G72" s="6">
+        <v>89.31999999999999</v>
+      </c>
+      <c r="H72" s="6">
         <v>89.89</v>
       </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="B72" s="6">
+      <c r="I72" s="6">
+        <v>89.95</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9">
+      <c r="A73" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B73" s="6">
         <v>88.86</v>
       </c>
-      <c r="C72" s="6">
+      <c r="C73" s="6">
+        <v>88.92</v>
+      </c>
+      <c r="D73" s="6">
         <v>89.13</v>
       </c>
-      <c r="D72" s="6">
+      <c r="E73" s="6">
+        <v>89.47</v>
+      </c>
+      <c r="F73" s="6">
         <v>89.03</v>
       </c>
-      <c r="E72" s="6">
+      <c r="G73" s="6">
+        <v>88.88</v>
+      </c>
+      <c r="H73" s="6">
         <v>89.37</v>
       </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="B73" s="6">
+      <c r="I73" s="6">
+        <v>89.51000000000001</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9">
+      <c r="A74" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B74" s="6">
         <v>87.02</v>
       </c>
-      <c r="C73" s="6">
+      <c r="C74" s="6">
+        <v>87.39</v>
+      </c>
+      <c r="D74" s="6">
         <v>86.39</v>
       </c>
-      <c r="D73" s="6">
+      <c r="E74" s="6">
+        <v>87.95</v>
+      </c>
+      <c r="F74" s="6">
         <v>87.77</v>
       </c>
-      <c r="E73" s="6">
+      <c r="G74" s="6">
+        <v>87.23999999999999</v>
+      </c>
+      <c r="H74" s="6">
         <v>87.51000000000001</v>
       </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="B74" s="6">
+      <c r="I74" s="6">
+        <v>88.11</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9">
+      <c r="A75" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B75" s="6">
         <v>79.97</v>
       </c>
-      <c r="C74" s="6">
+      <c r="C75" s="6">
+        <v>82.11</v>
+      </c>
+      <c r="D75" s="6">
         <v>76.53</v>
       </c>
-      <c r="D74" s="6">
+      <c r="E75" s="6">
+        <v>83.19</v>
+      </c>
+      <c r="F75" s="6">
         <v>83.81</v>
       </c>
-      <c r="E74" s="6">
+      <c r="G75" s="6">
+        <v>81.51000000000001</v>
+      </c>
+      <c r="H75" s="6">
         <v>81.09999999999999</v>
       </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="B75" s="6">
+      <c r="I75" s="6">
+        <v>83.91</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9">
+      <c r="A76" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B76" s="6">
         <v>23.89</v>
       </c>
-      <c r="C75" s="6">
+      <c r="C76" s="6">
+        <v>37.78</v>
+      </c>
+      <c r="D76" s="6">
         <v>19.09</v>
       </c>
-      <c r="D75" s="6">
+      <c r="E76" s="6">
+        <v>44.51</v>
+      </c>
+      <c r="F76" s="6">
         <v>48.79</v>
       </c>
-      <c r="E75" s="6">
+      <c r="G76" s="6">
+        <v>34.34</v>
+      </c>
+      <c r="H76" s="6">
         <v>35.4</v>
       </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="B76" s="6">
+      <c r="I76" s="6">
+        <v>48.96</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9">
+      <c r="A77" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B77" s="6">
         <v>8.279999999999999</v>
       </c>
-      <c r="C76" s="6">
+      <c r="C77" s="6">
+        <v>19.31</v>
+      </c>
+      <c r="D77" s="6">
         <v>6.02</v>
       </c>
-      <c r="D76" s="6">
+      <c r="E77" s="6">
+        <v>27.44</v>
+      </c>
+      <c r="F77" s="6">
         <v>31.08</v>
       </c>
-      <c r="E76" s="6">
+      <c r="G77" s="6">
+        <v>16.29</v>
+      </c>
+      <c r="H77" s="6">
         <v>18.09</v>
       </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="B77" s="6">
+      <c r="I77" s="6">
+        <v>32.88</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9">
+      <c r="A78" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="B78" s="6">
         <v>0.45096</v>
       </c>
-      <c r="C77" s="6">
+      <c r="C78" s="6">
+        <v>0.447948</v>
+      </c>
+      <c r="D78" s="6">
         <v>0.451708</v>
       </c>
-      <c r="D77" s="6">
+      <c r="E78" s="6">
+        <v>0.452289</v>
+      </c>
+      <c r="F78" s="6">
         <v>0.448684</v>
       </c>
-      <c r="E77" s="6">
+      <c r="G78" s="6">
+        <v>0.448064</v>
+      </c>
+      <c r="H78" s="6">
         <v>0.45364</v>
       </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="B78" s="6" t="e">
+      <c r="I78" s="6">
+        <v>0.452228</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9">
+      <c r="A79" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="B79" s="6" t="e">
         <f>#NUM!</f>
         <v>#NUM!</v>
       </c>
-      <c r="C78" s="6" t="e">
+      <c r="C79" s="6" t="e">
         <f>#NUM!</f>
         <v>#NUM!</v>
       </c>
-      <c r="D78" s="6" t="e">
+      <c r="D79" s="6" t="e">
         <f>#NUM!</f>
         <v>#NUM!</v>
       </c>
-      <c r="E78" s="6" t="e">
+      <c r="E79" s="6" t="e">
         <f>#NUM!</f>
         <v>#NUM!</v>
       </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="B79" s="4"/>
-      <c r="C79" s="4"/>
-      <c r="D79" s="4"/>
-      <c r="E79" s="4"/>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="B80" s="6">
+      <c r="F79" s="6" t="e">
+        <f>#NUM!</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="G79" s="6" t="e">
+        <f>#NUM!</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="H79" s="6" t="e">
+        <f>#NUM!</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="I79" s="6" t="e">
+        <f>#NUM!</f>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9">
+      <c r="A80" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B80" s="4"/>
+      <c r="C80" s="4"/>
+      <c r="D80" s="4"/>
+      <c r="E80" s="4"/>
+      <c r="F80" s="4"/>
+      <c r="G80" s="4"/>
+      <c r="H80" s="4"/>
+      <c r="I80" s="4"/>
+    </row>
+    <row r="81" spans="1:9">
+      <c r="A81" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="B81" s="6">
         <v>631556756</v>
       </c>
-      <c r="C80" s="6">
+      <c r="C81" s="6">
+        <v>764249459</v>
+      </c>
+      <c r="D81" s="6">
         <v>568035847</v>
       </c>
-      <c r="D80" s="6">
+      <c r="E81" s="6">
+        <v>822441819</v>
+      </c>
+      <c r="F81" s="6">
         <v>821386803</v>
       </c>
-      <c r="E80" s="6">
+      <c r="G81" s="6">
+        <v>716510178</v>
+      </c>
+      <c r="H81" s="6">
         <v>702597941</v>
       </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="B81" s="6">
+      <c r="I81" s="6">
+        <v>878231637</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9">
+      <c r="A82" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="B82" s="6">
         <v>85908429066</v>
       </c>
-      <c r="C81" s="6">
+      <c r="C82" s="6">
+        <v>102246216321</v>
+      </c>
+      <c r="D82" s="6">
         <v>78284529530</v>
       </c>
-      <c r="D81" s="6">
+      <c r="E82" s="6">
+        <v>109685009920</v>
+      </c>
+      <c r="F82" s="6">
         <v>110844458895</v>
       </c>
-      <c r="E81" s="6">
+      <c r="G82" s="6">
+        <v>95460670276</v>
+      </c>
+      <c r="H82" s="6">
         <v>96333319065</v>
       </c>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="B82" s="6">
+      <c r="I82" s="6">
+        <v>118151689028</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9">
+      <c r="A83" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="B83" s="6">
         <v>545857554</v>
       </c>
-      <c r="C82" s="6">
+      <c r="C83" s="6">
+        <v>657585375</v>
+      </c>
+      <c r="D83" s="6">
         <v>491101113</v>
       </c>
-      <c r="D82" s="6">
+      <c r="E83" s="6">
+        <v>701418679</v>
+      </c>
+      <c r="F83" s="6">
         <v>713083003</v>
       </c>
-      <c r="E82" s="6">
+      <c r="G83" s="6">
+        <v>619823015</v>
+      </c>
+      <c r="H83" s="6">
         <v>606738916</v>
       </c>
-    </row>
-    <row r="83" spans="1:5">
-      <c r="A83" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="B83" s="7">
+      <c r="I83" s="6">
+        <v>755498426</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9">
+      <c r="A84" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="B84" s="7">
         <v>0.8643048290025734</v>
       </c>
-      <c r="C83" s="7">
+      <c r="C84" s="7">
+        <v>0.8604328956417358</v>
+      </c>
+      <c r="D84" s="7">
         <v>0.8645600723857133</v>
       </c>
-      <c r="D83" s="7">
+      <c r="E84" s="7">
+        <v>0.8528489952673479</v>
+      </c>
+      <c r="F84" s="7">
         <v>0.8681451910300536</v>
       </c>
-      <c r="E83" s="7">
+      <c r="G84" s="7">
+        <v>0.8650582141486342</v>
+      </c>
+      <c r="H84" s="7">
         <v>0.8635648933676565</v>
       </c>
-    </row>
-    <row r="84" spans="1:5">
-      <c r="A84" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="B84" s="6">
+      <c r="I84" s="7">
+        <v>0.8602496131666912</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9">
+      <c r="A85" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="B85" s="6">
         <v>85699202</v>
       </c>
-      <c r="C84" s="6">
+      <c r="C85" s="6">
+        <v>106664084</v>
+      </c>
+      <c r="D85" s="6">
         <v>76934734</v>
       </c>
-      <c r="D84" s="6">
+      <c r="E85" s="6">
+        <v>121023140</v>
+      </c>
+      <c r="F85" s="6">
         <v>108303800</v>
       </c>
-      <c r="E84" s="6">
+      <c r="G85" s="6">
+        <v>96687163</v>
+      </c>
+      <c r="H85" s="6">
         <v>95859025</v>
       </c>
-    </row>
-    <row r="85" spans="1:5">
-      <c r="A85" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="B85" s="7">
+      <c r="I85" s="6">
+        <v>122733211</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9">
+      <c r="A86" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="B86" s="7">
         <v>0.1356951709974266</v>
       </c>
-      <c r="C85" s="7">
+      <c r="C86" s="7">
+        <v>0.1395671043582642</v>
+      </c>
+      <c r="D86" s="7">
         <v>0.1354399276142866</v>
       </c>
-      <c r="D85" s="7">
+      <c r="E86" s="7">
+        <v>0.1471510047326521</v>
+      </c>
+      <c r="F86" s="7">
         <v>0.1318548089699464</v>
       </c>
-      <c r="E85" s="7">
+      <c r="G86" s="7">
+        <v>0.1349417858513658</v>
+      </c>
+      <c r="H86" s="7">
         <v>0.1364351066323435</v>
       </c>
-    </row>
-    <row r="86" spans="1:5">
-      <c r="A86" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="B86" s="6">
+      <c r="I86" s="7">
+        <v>0.1397503868333088</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9">
+      <c r="A87" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="B87" s="6">
         <v>71284690</v>
       </c>
-      <c r="C86" s="6">
+      <c r="C87" s="6">
+        <v>88882892</v>
+      </c>
+      <c r="D87" s="6">
         <v>63391473</v>
       </c>
-      <c r="D86" s="6">
+      <c r="E87" s="6">
+        <v>100068114</v>
+      </c>
+      <c r="F87" s="6">
         <v>89691566</v>
       </c>
-      <c r="E86" s="6">
+      <c r="G87" s="6">
+        <v>80865384</v>
+      </c>
+      <c r="H87" s="6">
         <v>79763351</v>
       </c>
-    </row>
-    <row r="87" spans="1:5">
-      <c r="A87" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="B87" s="7">
+      <c r="I87" s="6">
+        <v>102407503</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9">
+      <c r="A88" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="B88" s="7">
         <v>0.8318010942505626</v>
       </c>
-      <c r="C87" s="7">
+      <c r="C88" s="7">
+        <v>0.8332972887106029</v>
+      </c>
+      <c r="D88" s="7">
         <v>0.8239642838045037</v>
       </c>
-      <c r="D87" s="7">
+      <c r="E88" s="7">
+        <v>0.8268510798843923</v>
+      </c>
+      <c r="F88" s="7">
         <v>0.8281479135542797</v>
       </c>
-      <c r="E87" s="7">
+      <c r="G88" s="7">
+        <v>0.8363611206587993</v>
+      </c>
+      <c r="H88" s="7">
         <v>0.8320901553087985</v>
       </c>
-    </row>
-    <row r="88" spans="1:5">
-      <c r="A88" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="B88" s="6">
+      <c r="I88" s="7">
+        <v>0.8343911331383647</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9">
+      <c r="A89" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="B89" s="6">
         <v>617142244</v>
       </c>
-      <c r="C88" s="6">
+      <c r="C89" s="6">
+        <v>746468267</v>
+      </c>
+      <c r="D89" s="6">
         <v>554492586</v>
       </c>
-      <c r="D88" s="6">
+      <c r="E89" s="6">
+        <v>801486793</v>
+      </c>
+      <c r="F89" s="6">
         <v>802774569</v>
       </c>
-      <c r="E88" s="6">
+      <c r="G89" s="6">
+        <v>700688399</v>
+      </c>
+      <c r="H89" s="6">
         <v>686502267</v>
       </c>
-    </row>
-    <row r="89" spans="1:5">
-      <c r="A89" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="B89" s="7">
+      <c r="I89" s="6">
+        <v>857905929</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9">
+      <c r="A90" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B90" s="7">
         <v>0.97717622072275</v>
       </c>
-      <c r="C89" s="7">
+      <c r="C90" s="7">
+        <v>0.9767337852966671</v>
+      </c>
+      <c r="D90" s="7">
         <v>0.9761577353409528</v>
       </c>
-      <c r="D89" s="7">
+      <c r="E90" s="7">
+        <v>0.9745209624366146</v>
+      </c>
+      <c r="F90" s="7">
         <v>0.9773404759706128</v>
       </c>
-      <c r="E89" s="7">
+      <c r="G90" s="7">
+        <v>0.9779182773869822</v>
+      </c>
+      <c r="H90" s="7">
         <v>0.9770912024349356</v>
       </c>
-    </row>
-    <row r="90" spans="1:5">
-      <c r="A90" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="B90" s="7">
+      <c r="I90" s="7">
+        <v>0.9768560967930605</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9">
+      <c r="A91" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="B91" s="7">
         <v>0.9613070880183131</v>
       </c>
-      <c r="C90" s="7">
+      <c r="C91" s="7">
+        <v>0.968841003176284</v>
+      </c>
+      <c r="D91" s="7">
         <v>0.9579217675545511</v>
       </c>
-      <c r="D90" s="7">
+      <c r="E91" s="7">
+        <v>0.9682436040636309</v>
+      </c>
+      <c r="F91" s="7">
         <v>0.9627340283376307</v>
       </c>
-      <c r="E90" s="7">
+      <c r="G91" s="7">
+        <v>0.9708405922950584</v>
+      </c>
+      <c r="H91" s="7">
         <v>0.9614665950970009</v>
       </c>
-    </row>
-    <row r="91" spans="1:5">
-      <c r="A91" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="B91" s="6">
+      <c r="I91" s="7">
+        <v>0.9696556362392232</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9">
+      <c r="A92" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="B92" s="6">
         <v>14414512</v>
       </c>
-      <c r="C91" s="6">
+      <c r="C92" s="6">
+        <v>17781192</v>
+      </c>
+      <c r="D92" s="6">
         <v>13543261</v>
       </c>
-      <c r="D91" s="6">
+      <c r="E92" s="6">
+        <v>20955026</v>
+      </c>
+      <c r="F92" s="6">
         <v>18612234</v>
       </c>
-      <c r="E91" s="6">
+      <c r="G92" s="6">
+        <v>15821779</v>
+      </c>
+      <c r="H92" s="6">
         <v>16095674</v>
       </c>
-    </row>
-    <row r="92" spans="1:5">
-      <c r="A92" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="B92" s="7">
+      <c r="I92" s="6">
+        <v>20325708</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9">
+      <c r="A93" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="B93" s="7">
         <v>0.02282377927724994</v>
       </c>
-      <c r="C92" s="7">
+      <c r="C93" s="7">
+        <v>0.02326621470333288</v>
+      </c>
+      <c r="D93" s="7">
         <v>0.02384226465904712</v>
       </c>
-      <c r="D92" s="7">
+      <c r="E93" s="7">
+        <v>0.02547903756338538</v>
+      </c>
+      <c r="F93" s="7">
         <v>0.02265952402938716</v>
       </c>
-      <c r="E92" s="7">
+      <c r="G93" s="7">
+        <v>0.02208172261301779</v>
+      </c>
+      <c r="H93" s="7">
         <v>0.02290879756506431</v>
       </c>
-    </row>
-    <row r="93" spans="1:5">
-      <c r="A93" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="B93" s="7">
+      <c r="I93" s="7">
+        <v>0.02314390320693947</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9">
+      <c r="A94" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B94" s="7">
         <v>0.9485702927519994</v>
       </c>
-      <c r="C93" s="7">
+      <c r="C94" s="7">
+        <v>0.9429681069596476</v>
+      </c>
+      <c r="D94" s="7">
         <v>0.9483884566304808</v>
       </c>
-      <c r="D93" s="7">
+      <c r="E94" s="7">
+        <v>0.937473112816399</v>
+      </c>
+      <c r="F94" s="7">
         <v>0.9492618777062415</v>
       </c>
-      <c r="E93" s="7">
+      <c r="G94" s="7">
+        <v>0.9441907202453467</v>
+      </c>
+      <c r="H94" s="7">
         <v>0.9484375390652902</v>
       </c>
-    </row>
-    <row r="94" spans="1:5">
-      <c r="A94" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="B94" s="7">
+      <c r="I94" s="7">
+        <v>0.9430292803397434</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9">
+      <c r="A95" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="B95" s="7">
         <v>0.840631</v>
       </c>
-      <c r="C94" s="7">
+      <c r="C95" s="7">
+        <v>0.828721</v>
+      </c>
+      <c r="D95" s="7">
         <v>0.849414</v>
       </c>
-      <c r="D94" s="7">
+      <c r="E95" s="7">
+        <v>0.822654</v>
+      </c>
+      <c r="F95" s="7">
         <v>0.835672</v>
       </c>
-      <c r="E94" s="7">
+      <c r="G95" s="7">
+        <v>0.827047</v>
+      </c>
+      <c r="H95" s="7">
         <v>0.847424</v>
       </c>
-    </row>
-    <row r="95" spans="1:5">
-      <c r="A95" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="B95" s="4"/>
-      <c r="C95" s="4"/>
-      <c r="D95" s="4"/>
-      <c r="E95" s="4"/>
-    </row>
-    <row r="96" spans="1:5">
-      <c r="A96" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="B96" s="6">
+      <c r="I95" s="7">
+        <v>0.834</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9">
+      <c r="A96" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B96" s="4"/>
+      <c r="C96" s="4"/>
+      <c r="D96" s="4"/>
+      <c r="E96" s="4"/>
+      <c r="F96" s="4"/>
+      <c r="G96" s="4"/>
+      <c r="H96" s="4"/>
+      <c r="I96" s="4"/>
+    </row>
+    <row r="97" spans="1:9">
+      <c r="A97" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="B97" s="6">
         <v>641982413</v>
       </c>
-      <c r="C96" s="6">
+      <c r="C97" s="6">
+        <v>770475511</v>
+      </c>
+      <c r="D97" s="6">
         <v>578849552</v>
       </c>
-      <c r="D96" s="6">
+      <c r="E97" s="6">
+        <v>827773909</v>
+      </c>
+      <c r="F97" s="6">
         <v>833848753</v>
       </c>
-      <c r="E96" s="6">
+      <c r="G97" s="6">
+        <v>721733727</v>
+      </c>
+      <c r="H97" s="6">
         <v>714015724</v>
       </c>
-    </row>
-    <row r="97" spans="1:5">
-      <c r="A97" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="B97" s="6">
+      <c r="I97" s="6">
+        <v>884753202</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9">
+      <c r="A98" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="B98" s="6">
         <v>10425657</v>
       </c>
-      <c r="C97" s="6">
+      <c r="C98" s="6">
+        <v>6226052</v>
+      </c>
+      <c r="D98" s="6">
         <v>10813705</v>
       </c>
-      <c r="D97" s="6">
+      <c r="E98" s="6">
+        <v>5332090</v>
+      </c>
+      <c r="F98" s="6">
         <v>12461950</v>
       </c>
-      <c r="E97" s="6">
+      <c r="G98" s="6">
+        <v>5223549</v>
+      </c>
+      <c r="H98" s="6">
         <v>11417783</v>
       </c>
-    </row>
-    <row r="98" spans="1:5">
-      <c r="A98" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="B98" s="6">
-        <v>96939344363</v>
-      </c>
-      <c r="C98" s="6">
-        <v>87406282352</v>
-      </c>
-      <c r="D98" s="6">
-        <v>125911161703</v>
-      </c>
-      <c r="E98" s="6">
-        <v>107816374324</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5">
+      <c r="I98" s="6">
+        <v>6521565</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9">
       <c r="A99" s="5" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="B99" s="6">
         <v>96939344363</v>
       </c>
       <c r="C99" s="6">
+        <v>116341802161</v>
+      </c>
+      <c r="D99" s="6">
         <v>87406282352</v>
       </c>
-      <c r="D99" s="6">
+      <c r="E99" s="6">
+        <v>124993860259</v>
+      </c>
+      <c r="F99" s="6">
         <v>125911161703</v>
       </c>
-      <c r="E99" s="6">
+      <c r="G99" s="6">
+        <v>108981792777</v>
+      </c>
+      <c r="H99" s="6">
         <v>107816374324</v>
       </c>
-    </row>
-    <row r="100" spans="1:5">
+      <c r="I99" s="6">
+        <v>133597733502</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9">
       <c r="A100" s="5" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B100" s="6">
+        <v>96939344363</v>
+      </c>
+      <c r="C100" s="6">
+        <v>116341802161</v>
+      </c>
+      <c r="D100" s="6">
+        <v>87406282352</v>
+      </c>
+      <c r="E100" s="6">
+        <v>124993860259</v>
+      </c>
+      <c r="F100" s="6">
+        <v>125911161703</v>
+      </c>
+      <c r="G100" s="6">
+        <v>108981792777</v>
+      </c>
+      <c r="H100" s="6">
+        <v>107816374324</v>
+      </c>
+      <c r="I100" s="6">
+        <v>133597733502</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9">
+      <c r="A101" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B101" s="6">
         <v>249580987</v>
       </c>
-      <c r="C100" s="6">
+      <c r="C101" s="6">
+        <v>319608830</v>
+      </c>
+      <c r="D101" s="6">
         <v>206848195</v>
       </c>
-      <c r="D100" s="6">
+      <c r="E101" s="6">
+        <v>345034518</v>
+      </c>
+      <c r="F101" s="6">
         <v>342276939</v>
       </c>
-      <c r="E100" s="6">
+      <c r="G101" s="6">
+        <v>307744169</v>
+      </c>
+      <c r="H101" s="6">
         <v>270131642</v>
       </c>
-    </row>
-    <row r="101" spans="1:5">
-      <c r="A101" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="B101" s="6">
+      <c r="I101" s="6">
+        <v>362403905</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9">
+      <c r="A102" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="B102" s="6">
         <v>265436971</v>
       </c>
-      <c r="C101" s="6">
+      <c r="C102" s="6">
+        <v>334564589</v>
+      </c>
+      <c r="D102" s="6">
         <v>222801274</v>
       </c>
-      <c r="D101" s="6">
+      <c r="E102" s="6">
+        <v>361826564</v>
+      </c>
+      <c r="F102" s="6">
         <v>361286223</v>
       </c>
-      <c r="E101" s="6">
+      <c r="G102" s="6">
+        <v>322084454</v>
+      </c>
+      <c r="H102" s="6">
         <v>288240203</v>
       </c>
-    </row>
-    <row r="102" spans="1:5">
-      <c r="A102" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="B102" s="6">
+      <c r="I102" s="6">
+        <v>380673162</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9">
+      <c r="A103" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="B103" s="6">
         <v>390413</v>
       </c>
-      <c r="C102" s="6">
+      <c r="C103" s="6">
+        <v>752648</v>
+      </c>
+      <c r="D103" s="6">
         <v>588188</v>
       </c>
-      <c r="D102" s="6">
+      <c r="E103" s="6">
+        <v>638150</v>
+      </c>
+      <c r="F103" s="6">
         <v>461771</v>
       </c>
-      <c r="E102" s="6">
+      <c r="G103" s="6">
+        <v>536920</v>
+      </c>
+      <c r="H103" s="6">
         <v>439907</v>
       </c>
-    </row>
-    <row r="103" spans="1:5">
-      <c r="A103" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="B103" s="6">
+      <c r="I103" s="6">
+        <v>771328</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9">
+      <c r="A104" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="B104" s="6">
         <v>10434797</v>
       </c>
-      <c r="C103" s="6">
+      <c r="C104" s="6">
+        <v>6300432</v>
+      </c>
+      <c r="D104" s="6">
         <v>10958162</v>
       </c>
-      <c r="D103" s="6">
+      <c r="E104" s="6">
+        <v>5435471</v>
+      </c>
+      <c r="F104" s="6">
         <v>12463412</v>
       </c>
-      <c r="E103" s="6">
+      <c r="G104" s="6">
+        <v>5222222</v>
+      </c>
+      <c r="H104" s="6">
         <v>11392974</v>
       </c>
-    </row>
-    <row r="104" spans="1:5">
-      <c r="A104" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="B104" s="7">
+      <c r="I104" s="6">
+        <v>6552875</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9">
+      <c r="A105" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="B105" s="7">
         <v>0.98376</v>
       </c>
-      <c r="C104" s="7">
+      <c r="C105" s="7">
+        <v>0.991919</v>
+      </c>
+      <c r="D105" s="7">
         <v>0.9813190000000001</v>
       </c>
-      <c r="D104" s="7">
+      <c r="E105" s="7">
+        <v>0.993559</v>
+      </c>
+      <c r="F105" s="7">
         <v>0.985055</v>
       </c>
-      <c r="E104" s="7">
+      <c r="G105" s="7">
+        <v>0.992762</v>
+      </c>
+      <c r="H105" s="7">
         <v>0.984009</v>
       </c>
-    </row>
-    <row r="105" spans="1:5">
-      <c r="A105" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="B105" s="7">
+      <c r="I105" s="7">
+        <v>0.992629</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9">
+      <c r="A106" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="B106" s="7">
         <v>0.886208</v>
       </c>
-      <c r="C105" s="7">
+      <c r="C106" s="7">
+        <v>0.878843</v>
+      </c>
+      <c r="D106" s="7">
         <v>0.89564</v>
       </c>
-      <c r="D105" s="7">
+      <c r="E106" s="7">
+        <v>0.8775230000000001</v>
+      </c>
+      <c r="F106" s="7">
         <v>0.880339</v>
       </c>
-      <c r="E105" s="7">
+      <c r="G106" s="7">
+        <v>0.875932</v>
+      </c>
+      <c r="H106" s="7">
         <v>0.893494</v>
+      </c>
+      <c r="I106" s="7">
+        <v>0.8843839999999999</v>
       </c>
     </row>
   </sheetData>
